--- a/research/traditional_assets/database/data/switzerland/switzerland_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_software_system_application.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1011486268241594</v>
+        <v>0.1010393798289961</v>
       </c>
       <c r="C2">
-        <v>5960.742973835262</v>
+        <v>5911.642335811643</v>
       </c>
       <c r="D2">
-        <v>5853.442973835262</v>
+        <v>5865.019335811642</v>
       </c>
       <c r="E2">
-        <v>-905.6</v>
+        <v>-844.923</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>60.67700000000001</v>
       </c>
       <c r="G2">
         <v>107.3</v>
@@ -1576,28 +1576,28 @@
         <v>213.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.0520531</v>
       </c>
       <c r="N2">
-        <v>213.4</v>
+        <v>210.3479469</v>
       </c>
       <c r="O2">
-        <v>31.1564</v>
+        <v>30.7108002474</v>
       </c>
       <c r="P2">
-        <v>182.2436</v>
+        <v>179.6371466526</v>
       </c>
       <c r="Q2">
-        <v>207.2436</v>
+        <v>204.6371466526</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1011486268241594</v>
+        <v>0.1016260786151476</v>
       </c>
       <c r="T2">
-        <v>1.278259280003682</v>
+        <v>1.289285880257451</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>69.92014654004545</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1010393798289961</v>
+        <v>0.1009301328338329</v>
       </c>
       <c r="C3">
-        <v>5911.642335811643</v>
+        <v>5862.587577697817</v>
       </c>
       <c r="D3">
-        <v>5865.019335811642</v>
+        <v>5876.641577697817</v>
       </c>
       <c r="E3">
-        <v>-844.923</v>
+        <v>-784.246</v>
       </c>
       <c r="F3">
-        <v>60.67700000000001</v>
+        <v>121.354</v>
       </c>
       <c r="G3">
         <v>107.3</v>
@@ -1658,28 +1658,28 @@
         <v>213.4</v>
       </c>
       <c r="M3">
-        <v>3.0520531</v>
+        <v>6.1041062</v>
       </c>
       <c r="N3">
-        <v>210.3479469</v>
+        <v>207.2958938</v>
       </c>
       <c r="O3">
-        <v>30.7108002474</v>
+        <v>30.2652004948</v>
       </c>
       <c r="P3">
-        <v>179.6371466526</v>
+        <v>177.0306933052</v>
       </c>
       <c r="Q3">
-        <v>204.6371466526</v>
+        <v>202.0306933052</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1016260786151476</v>
+        <v>0.1021132743202376</v>
       </c>
       <c r="T3">
-        <v>1.289285880257451</v>
+        <v>1.30053751316946</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>69.92014654004545</v>
+        <v>34.96007327002273</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1009301328338329</v>
+        <v>0.1008208858386696</v>
       </c>
       <c r="C4">
-        <v>5862.587577697817</v>
+        <v>5813.57897278505</v>
       </c>
       <c r="D4">
-        <v>5876.641577697817</v>
+        <v>5888.309972785049</v>
       </c>
       <c r="E4">
-        <v>-784.246</v>
+        <v>-723.569</v>
       </c>
       <c r="F4">
-        <v>121.354</v>
+        <v>182.031</v>
       </c>
       <c r="G4">
         <v>107.3</v>
@@ -1740,28 +1740,28 @@
         <v>213.4</v>
       </c>
       <c r="M4">
-        <v>6.1041062</v>
+        <v>9.156159300000001</v>
       </c>
       <c r="N4">
-        <v>207.2958938</v>
+        <v>204.2438407</v>
       </c>
       <c r="O4">
-        <v>30.2652004948</v>
+        <v>29.8196007422</v>
       </c>
       <c r="P4">
-        <v>177.0306933052</v>
+        <v>174.4242399578</v>
       </c>
       <c r="Q4">
-        <v>202.0306933052</v>
+        <v>199.4242399578</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1021132743202376</v>
+        <v>0.1026105152975975</v>
       </c>
       <c r="T4">
-        <v>1.30053751316946</v>
+        <v>1.312021138512645</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>34.96007327002273</v>
+        <v>23.30671551334848</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1008208858386696</v>
+        <v>0.1007116388435063</v>
       </c>
       <c r="C5">
-        <v>5813.57897278505</v>
+        <v>5764.616796539445</v>
       </c>
       <c r="D5">
-        <v>5888.309972785049</v>
+        <v>5900.024796539445</v>
       </c>
       <c r="E5">
-        <v>-723.569</v>
+        <v>-662.8920000000001</v>
       </c>
       <c r="F5">
-        <v>182.031</v>
+        <v>242.708</v>
       </c>
       <c r="G5">
         <v>107.3</v>
@@ -1822,28 +1822,28 @@
         <v>213.4</v>
       </c>
       <c r="M5">
-        <v>9.156159300000001</v>
+        <v>12.2082124</v>
       </c>
       <c r="N5">
-        <v>204.2438407</v>
+        <v>201.1917876</v>
       </c>
       <c r="O5">
-        <v>29.8196007422</v>
+        <v>29.3740009896</v>
       </c>
       <c r="P5">
-        <v>174.4242399578</v>
+        <v>171.8177866104</v>
       </c>
       <c r="Q5">
-        <v>199.4242399578</v>
+        <v>196.8177866104</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1026105152975975</v>
+        <v>0.1031181154619858</v>
       </c>
       <c r="T5">
-        <v>1.312021138512645</v>
+        <v>1.323744006050479</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>23.30671551334848</v>
+        <v>17.48003663501136</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1007116388435063</v>
+        <v>0.100602391848343</v>
       </c>
       <c r="C6">
-        <v>5764.616796539445</v>
+        <v>5715.701326623651</v>
       </c>
       <c r="D6">
-        <v>5900.024796539445</v>
+        <v>5911.786326623651</v>
       </c>
       <c r="E6">
-        <v>-662.8920000000001</v>
+        <v>-602.2149999999999</v>
       </c>
       <c r="F6">
-        <v>242.708</v>
+        <v>303.385</v>
       </c>
       <c r="G6">
         <v>107.3</v>
@@ -1904,28 +1904,28 @@
         <v>213.4</v>
       </c>
       <c r="M6">
-        <v>12.2082124</v>
+        <v>15.2602655</v>
       </c>
       <c r="N6">
-        <v>201.1917876</v>
+        <v>198.1397345</v>
       </c>
       <c r="O6">
-        <v>29.3740009896</v>
+        <v>28.928401237</v>
       </c>
       <c r="P6">
-        <v>171.8177866104</v>
+        <v>169.211333263</v>
       </c>
       <c r="Q6">
-        <v>196.8177866104</v>
+        <v>194.211333263</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1031181154619858</v>
+        <v>0.1036364019456243</v>
       </c>
       <c r="T6">
-        <v>1.323744006050479</v>
+        <v>1.335713670799637</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.48003663501136</v>
+        <v>13.98402930800909</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.100602391848343</v>
+        <v>0.1004931448531798</v>
       </c>
       <c r="C7">
-        <v>5715.701326623651</v>
+        <v>5666.832842918787</v>
       </c>
       <c r="D7">
-        <v>5911.786326623651</v>
+        <v>5923.594842918787</v>
       </c>
       <c r="E7">
-        <v>-602.2149999999999</v>
+        <v>-541.538</v>
       </c>
       <c r="F7">
-        <v>303.385</v>
+        <v>364.0620000000001</v>
       </c>
       <c r="G7">
         <v>107.3</v>
@@ -1986,28 +1986,28 @@
         <v>213.4</v>
       </c>
       <c r="M7">
-        <v>15.2602655</v>
+        <v>18.3123186</v>
       </c>
       <c r="N7">
-        <v>198.1397345</v>
+        <v>195.0876814</v>
       </c>
       <c r="O7">
-        <v>28.928401237</v>
+        <v>28.4828014844</v>
       </c>
       <c r="P7">
-        <v>169.211333263</v>
+        <v>166.6048799156</v>
       </c>
       <c r="Q7">
-        <v>194.211333263</v>
+        <v>191.6048799156</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1036364019456243</v>
+        <v>0.1041657158012551</v>
       </c>
       <c r="T7">
-        <v>1.335713670799637</v>
+        <v>1.347938009266861</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>13.98402930800909</v>
+        <v>11.65335775667424</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1004931448531798</v>
+        <v>0.1003838978580165</v>
       </c>
       <c r="C8">
-        <v>5666.832842918787</v>
+        <v>5618.011627546641</v>
       </c>
       <c r="D8">
-        <v>5923.594842918787</v>
+        <v>5935.450627546641</v>
       </c>
       <c r="E8">
-        <v>-541.538</v>
+        <v>-480.861</v>
       </c>
       <c r="F8">
-        <v>364.062</v>
+        <v>424.739</v>
       </c>
       <c r="G8">
         <v>107.3</v>
@@ -2068,28 +2068,28 @@
         <v>213.4</v>
       </c>
       <c r="M8">
-        <v>18.3123186</v>
+        <v>21.3643717</v>
       </c>
       <c r="N8">
-        <v>195.0876814</v>
+        <v>192.0356283</v>
       </c>
       <c r="O8">
-        <v>28.4828014844</v>
+        <v>28.0372017318</v>
       </c>
       <c r="P8">
-        <v>166.6048799156</v>
+        <v>163.9984265682</v>
       </c>
       <c r="Q8">
-        <v>191.6048799156</v>
+        <v>188.9984265682</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1041657158012551</v>
+        <v>0.1047064127505554</v>
       </c>
       <c r="T8">
-        <v>1.347938009266861</v>
+        <v>1.360425236733381</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.65335775667424</v>
+        <v>9.988592362863637</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1003838978580165</v>
+        <v>0.1003771308628532</v>
       </c>
       <c r="C9">
-        <v>5618.011627546641</v>
+        <v>5558.070561536822</v>
       </c>
       <c r="D9">
-        <v>5935.450627546641</v>
+        <v>5936.186561536822</v>
       </c>
       <c r="E9">
-        <v>-480.8609999999999</v>
+        <v>-420.184</v>
       </c>
       <c r="F9">
-        <v>424.7390000000001</v>
+        <v>485.4160000000001</v>
       </c>
       <c r="G9">
         <v>107.3</v>
@@ -2150,45 +2150,45 @@
         <v>213.4</v>
       </c>
       <c r="M9">
-        <v>21.3643717</v>
+        <v>25.1445488</v>
       </c>
       <c r="N9">
-        <v>192.0356283</v>
+        <v>188.2554512</v>
       </c>
       <c r="O9">
-        <v>28.0372017318</v>
+        <v>27.4852958752</v>
       </c>
       <c r="P9">
-        <v>163.9984265682</v>
+        <v>160.7701553248</v>
       </c>
       <c r="Q9">
-        <v>188.9984265682</v>
+        <v>185.7701553248</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1047064127505554</v>
+        <v>0.1052588639813622</v>
       </c>
       <c r="T9">
-        <v>1.360425236733381</v>
+        <v>1.373183925666564</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.146</v>
       </c>
       <c r="W9">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>9.988592362863635</v>
+        <v>8.486928983987177</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1003771308628532</v>
+        <v>0.10028069386769</v>
       </c>
       <c r="C10">
-        <v>5558.070561536822</v>
+        <v>5507.901283705587</v>
       </c>
       <c r="D10">
-        <v>5936.186561536822</v>
+        <v>5946.694283705587</v>
       </c>
       <c r="E10">
-        <v>-420.184</v>
+        <v>-359.5069999999999</v>
       </c>
       <c r="F10">
-        <v>485.4160000000001</v>
+        <v>546.0930000000001</v>
       </c>
       <c r="G10">
         <v>107.3</v>
@@ -2232,28 +2232,28 @@
         <v>213.4</v>
       </c>
       <c r="M10">
-        <v>25.1445488</v>
+        <v>28.2876174</v>
       </c>
       <c r="N10">
-        <v>188.2554512</v>
+        <v>185.1123826</v>
       </c>
       <c r="O10">
-        <v>27.4852958752</v>
+        <v>27.0264078596</v>
       </c>
       <c r="P10">
-        <v>160.7701553248</v>
+        <v>158.0859747404</v>
       </c>
       <c r="Q10">
-        <v>185.7701553248</v>
+        <v>183.0859747404</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1052588639813622</v>
+        <v>0.1058234569974615</v>
       </c>
       <c r="T10">
-        <v>1.373183925666564</v>
+        <v>1.386223025345531</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.486928983987177</v>
+        <v>7.543936874655268</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.10028069386769</v>
+        <v>0.1001842568725267</v>
       </c>
       <c r="C11">
-        <v>5507.901283705587</v>
+        <v>5457.769271554173</v>
       </c>
       <c r="D11">
-        <v>5946.694283705587</v>
+        <v>5957.239271554172</v>
       </c>
       <c r="E11">
-        <v>-359.5069999999999</v>
+        <v>-298.83</v>
       </c>
       <c r="F11">
-        <v>546.0930000000001</v>
+        <v>606.77</v>
       </c>
       <c r="G11">
         <v>107.3</v>
@@ -2314,28 +2314,28 @@
         <v>213.4</v>
       </c>
       <c r="M11">
-        <v>28.2876174</v>
+        <v>31.430686</v>
       </c>
       <c r="N11">
-        <v>185.1123826</v>
+        <v>181.969314</v>
       </c>
       <c r="O11">
-        <v>27.0264078596</v>
+        <v>26.567519844</v>
       </c>
       <c r="P11">
-        <v>158.0859747404</v>
+        <v>155.401794156</v>
       </c>
       <c r="Q11">
-        <v>183.0859747404</v>
+        <v>180.401794156</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1058234569974615</v>
+        <v>0.1064005965250296</v>
       </c>
       <c r="T11">
-        <v>1.386223025345531</v>
+        <v>1.399551882795142</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.543936874655268</v>
+        <v>6.789543187189742</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1001842568725267</v>
+        <v>0.1002475178773634</v>
       </c>
       <c r="C12">
-        <v>5457.769271554172</v>
+        <v>5390.170726604774</v>
       </c>
       <c r="D12">
-        <v>5957.239271554172</v>
+        <v>5950.317726604774</v>
       </c>
       <c r="E12">
-        <v>-298.8299999999999</v>
+        <v>-238.1529999999999</v>
       </c>
       <c r="F12">
-        <v>606.7700000000001</v>
+        <v>667.4470000000001</v>
       </c>
       <c r="G12">
         <v>107.3</v>
@@ -2396,45 +2396,45 @@
         <v>213.4</v>
       </c>
       <c r="M12">
-        <v>31.43068600000001</v>
+        <v>35.7084145</v>
       </c>
       <c r="N12">
-        <v>181.969314</v>
+        <v>177.6915855</v>
       </c>
       <c r="O12">
-        <v>26.567519844</v>
+        <v>25.942971483</v>
       </c>
       <c r="P12">
-        <v>155.401794156</v>
+        <v>151.748614017</v>
       </c>
       <c r="Q12">
-        <v>180.401794156</v>
+        <v>176.748614017</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1064005965250296</v>
+        <v>0.1069907054801836</v>
       </c>
       <c r="T12">
-        <v>1.399551882795142</v>
+        <v>1.413180265131261</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.146</v>
       </c>
       <c r="W12">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.789543187189741</v>
+        <v>5.976182448537444</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1002475178773634</v>
+        <v>0.1002475828822001</v>
       </c>
       <c r="C13">
-        <v>5390.170726604774</v>
+        <v>5329.486622534919</v>
       </c>
       <c r="D13">
-        <v>5950.317726604774</v>
+        <v>5950.310622534918</v>
       </c>
       <c r="E13">
-        <v>-238.1529999999999</v>
+        <v>-177.476</v>
       </c>
       <c r="F13">
-        <v>667.4470000000001</v>
+        <v>728.124</v>
       </c>
       <c r="G13">
         <v>107.3</v>
@@ -2478,45 +2478,45 @@
         <v>213.4</v>
       </c>
       <c r="M13">
-        <v>35.7084145</v>
+        <v>39.5371332</v>
       </c>
       <c r="N13">
-        <v>177.6915855</v>
+        <v>173.8628668</v>
       </c>
       <c r="O13">
-        <v>25.942971483</v>
+        <v>25.3839785528</v>
       </c>
       <c r="P13">
-        <v>151.748614017</v>
+        <v>148.4788882472</v>
       </c>
       <c r="Q13">
-        <v>176.748614017</v>
+        <v>173.4788882472</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1069907054801836</v>
+        <v>0.1075942260025002</v>
       </c>
       <c r="T13">
-        <v>1.413180265131261</v>
+        <v>1.427118383429565</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.146</v>
       </c>
       <c r="W13">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>5.976182448537444</v>
+        <v>5.397457598164958</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1002475828822001</v>
+        <v>0.1001724958870369</v>
       </c>
       <c r="C14">
-        <v>5329.486622534919</v>
+        <v>5277.026845924157</v>
       </c>
       <c r="D14">
-        <v>5950.310622534918</v>
+        <v>5958.527845924157</v>
       </c>
       <c r="E14">
-        <v>-177.476</v>
+        <v>-116.7989999999999</v>
       </c>
       <c r="F14">
-        <v>728.124</v>
+        <v>788.8010000000002</v>
       </c>
       <c r="G14">
         <v>107.3</v>
@@ -2560,28 +2560,28 @@
         <v>213.4</v>
       </c>
       <c r="M14">
-        <v>39.5371332</v>
+        <v>42.83189430000001</v>
       </c>
       <c r="N14">
-        <v>173.8628668</v>
+        <v>170.5681057</v>
       </c>
       <c r="O14">
-        <v>25.3839785528</v>
+        <v>24.9029434322</v>
       </c>
       <c r="P14">
-        <v>148.4788882472</v>
+        <v>145.6651622678</v>
       </c>
       <c r="Q14">
-        <v>173.4788882472</v>
+        <v>170.6651622678</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1075942260025002</v>
+        <v>0.1082116205598125</v>
       </c>
       <c r="T14">
-        <v>1.427118383429565</v>
+        <v>1.441376918240473</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.397457598164958</v>
+        <v>4.982268552152267</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1001724958870369</v>
+        <v>0.1000974088918736</v>
       </c>
       <c r="C15">
-        <v>5277.026845924157</v>
+        <v>5224.589796239983</v>
       </c>
       <c r="D15">
-        <v>5958.527845924157</v>
+        <v>5966.767796239983</v>
       </c>
       <c r="E15">
-        <v>-116.7989999999999</v>
+        <v>-56.12199999999984</v>
       </c>
       <c r="F15">
-        <v>788.8010000000002</v>
+        <v>849.4780000000002</v>
       </c>
       <c r="G15">
         <v>107.3</v>
@@ -2642,28 +2642,28 @@
         <v>213.4</v>
       </c>
       <c r="M15">
-        <v>42.83189430000001</v>
+        <v>46.12665540000001</v>
       </c>
       <c r="N15">
-        <v>170.5681057</v>
+        <v>167.2733446</v>
       </c>
       <c r="O15">
-        <v>24.9029434322</v>
+        <v>24.4219083116</v>
       </c>
       <c r="P15">
-        <v>145.6651622678</v>
+        <v>142.8514362884</v>
       </c>
       <c r="Q15">
-        <v>170.6651622678</v>
+        <v>167.8514362884</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1082116205598125</v>
+        <v>0.1088433731300856</v>
       </c>
       <c r="T15">
-        <v>1.441376918240473</v>
+        <v>1.455967046884194</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.982268552152267</v>
+        <v>4.626392226998535</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1000974088918736</v>
+        <v>0.1000223218967103</v>
       </c>
       <c r="C16">
-        <v>5224.589796239983</v>
+        <v>5172.175567899043</v>
       </c>
       <c r="D16">
-        <v>5966.767796239983</v>
+        <v>5975.030567899043</v>
       </c>
       <c r="E16">
-        <v>-56.12199999999984</v>
+        <v>4.555000000000177</v>
       </c>
       <c r="F16">
-        <v>849.4780000000002</v>
+        <v>910.1550000000002</v>
       </c>
       <c r="G16">
         <v>107.3</v>
@@ -2724,28 +2724,28 @@
         <v>213.4</v>
       </c>
       <c r="M16">
-        <v>46.12665540000001</v>
+        <v>49.42141650000001</v>
       </c>
       <c r="N16">
-        <v>167.2733446</v>
+        <v>163.9785835</v>
       </c>
       <c r="O16">
-        <v>24.4219083116</v>
+        <v>23.940873191</v>
       </c>
       <c r="P16">
-        <v>142.8514362884</v>
+        <v>140.037710309</v>
       </c>
       <c r="Q16">
-        <v>167.8514362884</v>
+        <v>165.037710309</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1088433731300856</v>
+        <v>0.109489990466718</v>
       </c>
       <c r="T16">
-        <v>1.455967046884194</v>
+        <v>1.470900472672472</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.626392226998535</v>
+        <v>4.317966078531965</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1000223218967103</v>
+        <v>0.1000838749015471</v>
       </c>
       <c r="C17">
-        <v>5172.175567899043</v>
+        <v>5104.723423602279</v>
       </c>
       <c r="D17">
-        <v>5975.030567899043</v>
+        <v>5968.255423602279</v>
       </c>
       <c r="E17">
-        <v>4.555000000000064</v>
+        <v>65.23200000000008</v>
       </c>
       <c r="F17">
-        <v>910.1550000000001</v>
+        <v>970.8320000000001</v>
       </c>
       <c r="G17">
         <v>107.3</v>
@@ -2806,45 +2806,45 @@
         <v>213.4</v>
       </c>
       <c r="M17">
-        <v>49.42141650000001</v>
+        <v>53.68700960000001</v>
       </c>
       <c r="N17">
-        <v>163.9785835</v>
+        <v>159.7129904</v>
       </c>
       <c r="O17">
-        <v>23.940873191</v>
+        <v>23.3180965984</v>
       </c>
       <c r="P17">
-        <v>140.037710309</v>
+        <v>136.3948938016</v>
       </c>
       <c r="Q17">
-        <v>165.037710309</v>
+        <v>161.3948938016</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.109489990466718</v>
+        <v>0.1101520034542227</v>
       </c>
       <c r="T17">
-        <v>1.470900472672472</v>
+        <v>1.486189456217614</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.146</v>
       </c>
       <c r="W17">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.317966078531966</v>
+        <v>3.974890789968677</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1000838749015471</v>
+        <v>0.1000173279063838</v>
       </c>
       <c r="C18">
-        <v>5104.723423602279</v>
+        <v>5051.371931519111</v>
       </c>
       <c r="D18">
-        <v>5968.255423602279</v>
+        <v>5975.580931519111</v>
       </c>
       <c r="E18">
-        <v>65.23200000000008</v>
+        <v>125.9090000000002</v>
       </c>
       <c r="F18">
-        <v>970.8320000000001</v>
+        <v>1031.509</v>
       </c>
       <c r="G18">
         <v>107.3</v>
@@ -2888,28 +2888,28 @@
         <v>213.4</v>
       </c>
       <c r="M18">
-        <v>53.68700960000001</v>
+        <v>57.04244770000002</v>
       </c>
       <c r="N18">
-        <v>159.7129904</v>
+        <v>156.3575523</v>
       </c>
       <c r="O18">
-        <v>23.3180965984</v>
+        <v>22.8282026358</v>
       </c>
       <c r="P18">
-        <v>136.3948938016</v>
+        <v>133.5293496642</v>
       </c>
       <c r="Q18">
-        <v>161.3948938016</v>
+        <v>158.5293496642</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1101520034542227</v>
+        <v>0.1108299685619082</v>
       </c>
       <c r="T18">
-        <v>1.486189456217614</v>
+        <v>1.501846849004808</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.974890789968677</v>
+        <v>3.741073684676401</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1000173279063838</v>
+        <v>0.09995078091122049</v>
       </c>
       <c r="C19">
-        <v>5051.371931519111</v>
+        <v>4998.038444367052</v>
       </c>
       <c r="D19">
-        <v>5975.580931519111</v>
+        <v>5982.924444367052</v>
       </c>
       <c r="E19">
-        <v>125.9090000000002</v>
+        <v>186.5860000000001</v>
       </c>
       <c r="F19">
-        <v>1031.509</v>
+        <v>1092.186</v>
       </c>
       <c r="G19">
         <v>107.3</v>
@@ -2970,28 +2970,28 @@
         <v>213.4</v>
       </c>
       <c r="M19">
-        <v>57.04244770000002</v>
+        <v>60.39788580000001</v>
       </c>
       <c r="N19">
-        <v>156.3575523</v>
+        <v>153.0021142</v>
       </c>
       <c r="O19">
-        <v>22.8282026358</v>
+        <v>22.3383086732</v>
       </c>
       <c r="P19">
-        <v>133.5293496642</v>
+        <v>130.6638055268</v>
       </c>
       <c r="Q19">
-        <v>158.5293496642</v>
+        <v>155.6638055268</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1108299685619082</v>
+        <v>0.1115244694039274</v>
       </c>
       <c r="T19">
-        <v>1.501846849004808</v>
+        <v>1.517886129420957</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.741073684676401</v>
+        <v>3.533236257749935</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0999507809112205</v>
+        <v>0.09988423391605725</v>
       </c>
       <c r="C20">
-        <v>4998.038444367052</v>
+        <v>4944.723028607652</v>
       </c>
       <c r="D20">
-        <v>5982.924444367051</v>
+        <v>5990.286028607652</v>
       </c>
       <c r="E20">
-        <v>186.5860000000001</v>
+        <v>247.263</v>
       </c>
       <c r="F20">
-        <v>1092.186</v>
+        <v>1152.863</v>
       </c>
       <c r="G20">
         <v>107.3</v>
@@ -3052,28 +3052,28 @@
         <v>213.4</v>
       </c>
       <c r="M20">
-        <v>60.39788580000001</v>
+        <v>63.75332390000001</v>
       </c>
       <c r="N20">
-        <v>153.0021142</v>
+        <v>149.6466761</v>
       </c>
       <c r="O20">
-        <v>22.3383086732</v>
+        <v>21.8484147106</v>
       </c>
       <c r="P20">
-        <v>130.6638055268</v>
+        <v>127.7982613894</v>
       </c>
       <c r="Q20">
-        <v>155.6638055268</v>
+        <v>152.7982613894</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1115244694039274</v>
+        <v>0.1122361184148855</v>
       </c>
       <c r="T20">
-        <v>1.517886129420957</v>
+        <v>1.534321441452321</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.533236257749935</v>
+        <v>3.347276454710466</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09988423391605725</v>
+        <v>0.09981768692089396</v>
       </c>
       <c r="C21">
-        <v>4944.723028607652</v>
+        <v>4891.425751029981</v>
       </c>
       <c r="D21">
-        <v>5990.286028607652</v>
+        <v>5997.665751029981</v>
       </c>
       <c r="E21">
-        <v>247.263</v>
+        <v>307.9400000000002</v>
       </c>
       <c r="F21">
-        <v>1152.863</v>
+        <v>1213.54</v>
       </c>
       <c r="G21">
         <v>107.3</v>
@@ -3134,28 +3134,28 @@
         <v>213.4</v>
       </c>
       <c r="M21">
-        <v>63.75332390000001</v>
+        <v>67.10876200000001</v>
       </c>
       <c r="N21">
-        <v>149.6466761</v>
+        <v>146.291238</v>
       </c>
       <c r="O21">
-        <v>21.8484147106</v>
+        <v>21.358520748</v>
       </c>
       <c r="P21">
-        <v>127.7982613894</v>
+        <v>124.932717252</v>
       </c>
       <c r="Q21">
-        <v>152.7982613894</v>
+        <v>149.932717252</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1122361184148855</v>
+        <v>0.1129655586511175</v>
       </c>
       <c r="T21">
-        <v>1.534321441452321</v>
+        <v>1.551167636284468</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.347276454710466</v>
+        <v>3.179912631974942</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09981768692089396</v>
+        <v>0.09975113992573068</v>
       </c>
       <c r="C22">
-        <v>4891.425751029981</v>
+        <v>4838.146678752623</v>
       </c>
       <c r="D22">
-        <v>5997.665751029981</v>
+        <v>6005.063678752624</v>
       </c>
       <c r="E22">
-        <v>307.9400000000002</v>
+        <v>368.6170000000003</v>
       </c>
       <c r="F22">
-        <v>1213.54</v>
+        <v>1274.217</v>
       </c>
       <c r="G22">
         <v>107.3</v>
@@ -3216,28 +3216,28 @@
         <v>213.4</v>
       </c>
       <c r="M22">
-        <v>67.10876200000001</v>
+        <v>70.46420010000001</v>
       </c>
       <c r="N22">
-        <v>146.291238</v>
+        <v>142.9357999</v>
       </c>
       <c r="O22">
-        <v>21.358520748</v>
+        <v>20.8686267854</v>
       </c>
       <c r="P22">
-        <v>124.932717252</v>
+        <v>122.0671731146</v>
       </c>
       <c r="Q22">
-        <v>149.932717252</v>
+        <v>147.0671731146</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1129655586511175</v>
+        <v>0.113713465728773</v>
       </c>
       <c r="T22">
-        <v>1.551167636284468</v>
+        <v>1.568440317061733</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.179912631974942</v>
+        <v>3.028488220928516</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09975113992573068</v>
+        <v>0.1001542929305674</v>
       </c>
       <c r="C23">
-        <v>4838.146678752624</v>
+        <v>4732.92932442555</v>
       </c>
       <c r="D23">
-        <v>6005.063678752624</v>
+        <v>5960.523324425551</v>
       </c>
       <c r="E23">
-        <v>368.6170000000001</v>
+        <v>429.2940000000002</v>
       </c>
       <c r="F23">
-        <v>1274.217</v>
+        <v>1334.894</v>
       </c>
       <c r="G23">
         <v>107.3</v>
@@ -3298,45 +3298,45 @@
         <v>213.4</v>
       </c>
       <c r="M23">
-        <v>70.46420010000001</v>
+        <v>77.15687320000002</v>
       </c>
       <c r="N23">
-        <v>142.9357999</v>
+        <v>136.2431268</v>
       </c>
       <c r="O23">
-        <v>20.8686267854</v>
+        <v>19.89149651279999</v>
       </c>
       <c r="P23">
-        <v>122.0671731146</v>
+        <v>116.3516302872</v>
       </c>
       <c r="Q23">
-        <v>147.0671731146</v>
+        <v>141.3516302872</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.113713465728773</v>
+        <v>0.1144805499109839</v>
       </c>
       <c r="T23">
-        <v>1.568440317061733</v>
+        <v>1.586155887089697</v>
       </c>
       <c r="U23">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V23">
         <v>0.146</v>
       </c>
       <c r="W23">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.028488220928516</v>
+        <v>2.76579378024873</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1001542929305674</v>
+        <v>0.1001090959354042</v>
       </c>
       <c r="C24">
-        <v>4732.92932442555</v>
+        <v>4677.212777904374</v>
       </c>
       <c r="D24">
-        <v>5960.523324425551</v>
+        <v>5965.483777904374</v>
       </c>
       <c r="E24">
-        <v>429.2940000000002</v>
+        <v>489.9710000000001</v>
       </c>
       <c r="F24">
-        <v>1334.894</v>
+        <v>1395.571</v>
       </c>
       <c r="G24">
         <v>107.3</v>
@@ -3380,28 +3380,28 @@
         <v>213.4</v>
       </c>
       <c r="M24">
-        <v>77.15687320000002</v>
+        <v>80.66400380000002</v>
       </c>
       <c r="N24">
-        <v>136.2431268</v>
+        <v>132.7359962</v>
       </c>
       <c r="O24">
-        <v>19.89149651279999</v>
+        <v>19.3794554452</v>
       </c>
       <c r="P24">
-        <v>116.3516302872</v>
+        <v>113.3565407548</v>
       </c>
       <c r="Q24">
-        <v>141.3516302872</v>
+        <v>138.3565407548</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1144805499109839</v>
+        <v>0.1152675583576677</v>
       </c>
       <c r="T24">
-        <v>1.586155887089697</v>
+        <v>1.604331601793712</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.76579378024873</v>
+        <v>2.645541876759655</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1001090959354042</v>
+        <v>0.1000638989402409</v>
       </c>
       <c r="C25">
-        <v>4677.212777904374</v>
+        <v>4621.504494615157</v>
       </c>
       <c r="D25">
-        <v>5965.483777904374</v>
+        <v>5970.452494615157</v>
       </c>
       <c r="E25">
-        <v>489.9710000000001</v>
+        <v>550.6480000000003</v>
       </c>
       <c r="F25">
-        <v>1395.571</v>
+        <v>1456.248</v>
       </c>
       <c r="G25">
         <v>107.3</v>
@@ -3462,28 +3462,28 @@
         <v>213.4</v>
       </c>
       <c r="M25">
-        <v>80.66400380000002</v>
+        <v>84.17113440000003</v>
       </c>
       <c r="N25">
-        <v>132.7359962</v>
+        <v>129.2288656</v>
       </c>
       <c r="O25">
-        <v>19.3794554452</v>
+        <v>18.8674143776</v>
       </c>
       <c r="P25">
-        <v>113.3565407548</v>
+        <v>110.3614512224</v>
       </c>
       <c r="Q25">
-        <v>138.3565407548</v>
+        <v>135.3614512224</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1152675583576677</v>
+        <v>0.1160752775529485</v>
       </c>
       <c r="T25">
-        <v>1.604331601793712</v>
+        <v>1.622985624779412</v>
       </c>
       <c r="U25">
         <v>0.0578</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.645541876759655</v>
+        <v>2.535310965228002</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1000638989402409</v>
+        <v>0.1007659519450776</v>
       </c>
       <c r="C26">
-        <v>4621.504494615157</v>
+        <v>4484.569848458717</v>
       </c>
       <c r="D26">
-        <v>5970.452494615157</v>
+        <v>5894.194848458717</v>
       </c>
       <c r="E26">
-        <v>550.648</v>
+        <v>611.3250000000002</v>
       </c>
       <c r="F26">
-        <v>1456.248</v>
+        <v>1516.925</v>
       </c>
       <c r="G26">
         <v>107.3</v>
@@ -3544,45 +3544,45 @@
         <v>213.4</v>
       </c>
       <c r="M26">
-        <v>84.17113440000001</v>
+        <v>92.98750250000001</v>
       </c>
       <c r="N26">
-        <v>129.2288656</v>
+        <v>120.4124975</v>
       </c>
       <c r="O26">
-        <v>18.8674143776</v>
+        <v>17.580224635</v>
       </c>
       <c r="P26">
-        <v>110.3614512224</v>
+        <v>102.832272865</v>
       </c>
       <c r="Q26">
-        <v>135.3614512224</v>
+        <v>127.832272865</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1160752775529485</v>
+        <v>0.1169045359267701</v>
       </c>
       <c r="T26">
-        <v>1.622985624779412</v>
+        <v>1.642137088378063</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.146</v>
       </c>
       <c r="W26">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.535310965228003</v>
+        <v>2.294932052831508</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1007659519450776</v>
+        <v>0.1013723569499143</v>
       </c>
       <c r="C27">
-        <v>4484.569848458717</v>
+        <v>4359.575453052767</v>
       </c>
       <c r="D27">
-        <v>5894.194848458717</v>
+        <v>5829.877453052767</v>
       </c>
       <c r="E27">
-        <v>611.3250000000002</v>
+        <v>672.0020000000003</v>
       </c>
       <c r="F27">
-        <v>1516.925</v>
+        <v>1577.602</v>
       </c>
       <c r="G27">
         <v>107.3</v>
@@ -3626,45 +3626,45 @@
         <v>213.4</v>
       </c>
       <c r="M27">
-        <v>92.98750250000001</v>
+        <v>101.1242882</v>
       </c>
       <c r="N27">
-        <v>120.4124975</v>
+        <v>112.2757118</v>
       </c>
       <c r="O27">
-        <v>17.580224635</v>
+        <v>16.39225392279999</v>
       </c>
       <c r="P27">
-        <v>102.832272865</v>
+        <v>95.88345787719999</v>
       </c>
       <c r="Q27">
-        <v>127.832272865</v>
+        <v>120.8834578772</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1169045359267701</v>
+        <v>0.1177562066890734</v>
       </c>
       <c r="T27">
-        <v>1.642137088378063</v>
+        <v>1.661806159101003</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.146</v>
       </c>
       <c r="W27">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.294932052831508</v>
+        <v>2.110274433555913</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1013723569499143</v>
+        <v>0.101380961954751</v>
       </c>
       <c r="C28">
-        <v>4359.575453052767</v>
+        <v>4297.99587558889</v>
       </c>
       <c r="D28">
-        <v>5829.877453052767</v>
+        <v>5828.97487558889</v>
       </c>
       <c r="E28">
-        <v>672.0020000000003</v>
+        <v>732.6790000000002</v>
       </c>
       <c r="F28">
-        <v>1577.602</v>
+        <v>1638.279</v>
       </c>
       <c r="G28">
         <v>107.3</v>
@@ -3708,28 +3708,28 @@
         <v>213.4</v>
       </c>
       <c r="M28">
-        <v>101.1242882</v>
+        <v>105.0136839</v>
       </c>
       <c r="N28">
-        <v>112.2757118</v>
+        <v>108.3863161</v>
       </c>
       <c r="O28">
-        <v>16.39225392279999</v>
+        <v>15.8244021506</v>
       </c>
       <c r="P28">
-        <v>95.88345787719999</v>
+        <v>92.56191394939999</v>
       </c>
       <c r="Q28">
-        <v>120.8834578772</v>
+        <v>117.5619139494</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1177562066890734</v>
+        <v>0.1186312108969192</v>
       </c>
       <c r="T28">
-        <v>1.661806159101003</v>
+        <v>1.682014108473886</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.110274433555913</v>
+        <v>2.032116121201991</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.101380961954751</v>
+        <v>0.1041872709595878</v>
       </c>
       <c r="C29">
-        <v>4297.99587558889</v>
+        <v>3957.156703021276</v>
       </c>
       <c r="D29">
-        <v>5828.97487558889</v>
+        <v>5548.812703021276</v>
       </c>
       <c r="E29">
-        <v>732.6790000000002</v>
+        <v>793.3560000000003</v>
       </c>
       <c r="F29">
-        <v>1638.279</v>
+        <v>1698.956</v>
       </c>
       <c r="G29">
         <v>107.3</v>
@@ -3790,45 +3790,45 @@
         <v>213.4</v>
       </c>
       <c r="M29">
-        <v>105.0136839</v>
+        <v>128.7808648</v>
       </c>
       <c r="N29">
-        <v>108.3863161</v>
+        <v>84.61913519999996</v>
       </c>
       <c r="O29">
-        <v>15.8244021506</v>
+        <v>12.35439373919999</v>
       </c>
       <c r="P29">
-        <v>92.56191394939999</v>
+        <v>72.26474146079997</v>
       </c>
       <c r="Q29">
-        <v>117.5619139494</v>
+        <v>97.26474146079997</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1186312108969192</v>
+        <v>0.1195305207772052</v>
       </c>
       <c r="T29">
-        <v>1.682014108473886</v>
+        <v>1.702783389773794</v>
       </c>
       <c r="U29">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
         <v>0.146</v>
       </c>
       <c r="W29">
-        <v>0.0547414</v>
+        <v>0.0647332</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.032116121201991</v>
+        <v>1.657078482361612</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1041872709595878</v>
+        <v>0.1042957939644245</v>
       </c>
       <c r="C30">
-        <v>3957.156703021276</v>
+        <v>3886.185393174412</v>
       </c>
       <c r="D30">
-        <v>5548.812703021276</v>
+        <v>5538.518393174412</v>
       </c>
       <c r="E30">
-        <v>793.3560000000003</v>
+        <v>854.0330000000005</v>
       </c>
       <c r="F30">
-        <v>1698.956</v>
+        <v>1759.633</v>
       </c>
       <c r="G30">
         <v>107.3</v>
@@ -3872,28 +3872,28 @@
         <v>213.4</v>
       </c>
       <c r="M30">
-        <v>128.7808648</v>
+        <v>133.3801814000001</v>
       </c>
       <c r="N30">
-        <v>84.61913519999996</v>
+        <v>80.01981859999995</v>
       </c>
       <c r="O30">
-        <v>12.35439373919999</v>
+        <v>11.68289351559999</v>
       </c>
       <c r="P30">
-        <v>72.26474146079997</v>
+        <v>68.33692508439995</v>
       </c>
       <c r="Q30">
-        <v>97.26474146079997</v>
+        <v>93.33692508439995</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1195305207772052</v>
+        <v>0.1204551633301754</v>
       </c>
       <c r="T30">
-        <v>1.702783389773794</v>
+        <v>1.724137721251163</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.657078482361612</v>
+        <v>1.599937845038798</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1042957939644245</v>
+        <v>0.1044043169692612</v>
       </c>
       <c r="C31">
-        <v>3886.185393174413</v>
+        <v>3815.252209168616</v>
       </c>
       <c r="D31">
-        <v>5538.518393174412</v>
+        <v>5528.262209168616</v>
       </c>
       <c r="E31">
-        <v>854.033</v>
+        <v>914.7100000000002</v>
       </c>
       <c r="F31">
-        <v>1759.633</v>
+        <v>1820.31</v>
       </c>
       <c r="G31">
         <v>107.3</v>
@@ -3954,28 +3954,28 @@
         <v>213.4</v>
       </c>
       <c r="M31">
-        <v>133.3801814</v>
+        <v>137.979498</v>
       </c>
       <c r="N31">
-        <v>80.01981859999998</v>
+        <v>75.42050199999997</v>
       </c>
       <c r="O31">
-        <v>11.6828935156</v>
+        <v>11.011393292</v>
       </c>
       <c r="P31">
-        <v>68.33692508439998</v>
+        <v>64.40910870799998</v>
       </c>
       <c r="Q31">
-        <v>93.33692508439998</v>
+        <v>89.40910870799998</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1204551633301754</v>
+        <v>0.1214062242418018</v>
       </c>
       <c r="T31">
-        <v>1.724137721251163</v>
+        <v>1.74610217648503</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.599937845038798</v>
+        <v>1.546606583537505</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1044043169692612</v>
+        <v>0.108272147974098</v>
       </c>
       <c r="C32">
-        <v>3815.252209168616</v>
+        <v>3412.304538655492</v>
       </c>
       <c r="D32">
-        <v>5528.262209168616</v>
+        <v>5185.991538655492</v>
       </c>
       <c r="E32">
-        <v>914.7100000000002</v>
+        <v>975.3870000000003</v>
       </c>
       <c r="F32">
-        <v>1820.31</v>
+        <v>1880.987</v>
       </c>
       <c r="G32">
         <v>107.3</v>
@@ -4036,45 +4036,45 @@
         <v>213.4</v>
       </c>
       <c r="M32">
-        <v>137.979498</v>
+        <v>169.28883</v>
       </c>
       <c r="N32">
-        <v>75.42050199999997</v>
+        <v>44.11116999999999</v>
       </c>
       <c r="O32">
-        <v>11.011393292</v>
+        <v>6.440230819999997</v>
       </c>
       <c r="P32">
-        <v>64.40910870799998</v>
+        <v>37.67093917999999</v>
       </c>
       <c r="Q32">
-        <v>89.40910870799998</v>
+        <v>62.67093917999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1214062242418018</v>
+        <v>0.1223848521363738</v>
       </c>
       <c r="T32">
-        <v>1.74610217648503</v>
+        <v>1.76870328259524</v>
       </c>
       <c r="U32">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.546606583537505</v>
+        <v>1.260567516474655</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.108272147974098</v>
+        <v>0.1169135082339718</v>
       </c>
       <c r="C33">
-        <v>3412.304538655492</v>
+        <v>2721.45160860946</v>
       </c>
       <c r="D33">
-        <v>5185.991538655492</v>
+        <v>4555.81560860946</v>
       </c>
       <c r="E33">
-        <v>975.3870000000003</v>
+        <v>1036.064</v>
       </c>
       <c r="F33">
-        <v>1880.987</v>
+        <v>1941.664</v>
       </c>
       <c r="G33">
         <v>107.3</v>
@@ -4118,45 +4118,45 @@
         <v>213.4</v>
       </c>
       <c r="M33">
-        <v>169.28883</v>
+        <v>230.2813504</v>
       </c>
       <c r="N33">
-        <v>44.11116999999999</v>
+        <v>-16.88135040000003</v>
       </c>
       <c r="O33">
-        <v>6.440230819999997</v>
+        <v>-2.464677158400004</v>
       </c>
       <c r="P33">
-        <v>37.67093917999999</v>
+        <v>-14.41667324160003</v>
       </c>
       <c r="Q33">
-        <v>62.67093917999999</v>
+        <v>10.58332675839997</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1223848521363738</v>
+        <v>0.1236710352287936</v>
       </c>
       <c r="T33">
-        <v>1.76870328259524</v>
+        <v>1.798407280110706</v>
       </c>
       <c r="U33">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V33">
-        <v>0.146</v>
+        <v>0.1352971048062779</v>
       </c>
       <c r="W33">
-        <v>0.07686</v>
+        <v>0.1025537633699755</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.260567516474655</v>
+        <v>0.926692498673136</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1169135082339718</v>
+        <v>0.1176415082339718</v>
       </c>
       <c r="C34">
-        <v>2721.45160860946</v>
+        <v>2614.608626789225</v>
       </c>
       <c r="D34">
-        <v>4555.81560860946</v>
+        <v>4509.649626789225</v>
       </c>
       <c r="E34">
-        <v>1036.064</v>
+        <v>1096.741</v>
       </c>
       <c r="F34">
-        <v>1941.664</v>
+        <v>2002.341</v>
       </c>
       <c r="G34">
         <v>107.3</v>
@@ -4200,37 +4200,37 @@
         <v>213.4</v>
       </c>
       <c r="M34">
-        <v>230.2813504</v>
+        <v>237.4776426000001</v>
       </c>
       <c r="N34">
-        <v>-16.88135040000003</v>
+        <v>-24.07764260000005</v>
       </c>
       <c r="O34">
-        <v>-2.464677158400004</v>
+        <v>-3.515335819600007</v>
       </c>
       <c r="P34">
-        <v>-14.41667324160003</v>
+        <v>-20.56230678040004</v>
       </c>
       <c r="Q34">
-        <v>10.58332675839997</v>
+        <v>4.437693219599961</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1236710352287936</v>
+        <v>0.1248332894859397</v>
       </c>
       <c r="T34">
-        <v>1.798407280110706</v>
+        <v>1.825249179813851</v>
       </c>
       <c r="U34">
         <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.1352971048062779</v>
+        <v>0.1311971925394209</v>
       </c>
       <c r="W34">
-        <v>0.1025537633699755</v>
+        <v>0.1030400129648247</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.926692498673136</v>
+        <v>0.898610907804253</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1176415082339718</v>
+        <v>0.1183695082339718</v>
       </c>
       <c r="C35">
-        <v>2614.608626789225</v>
+        <v>2508.691897208617</v>
       </c>
       <c r="D35">
-        <v>4509.649626789225</v>
+        <v>4464.409897208618</v>
       </c>
       <c r="E35">
-        <v>1096.741</v>
+        <v>1157.418000000001</v>
       </c>
       <c r="F35">
-        <v>2002.341</v>
+        <v>2063.018</v>
       </c>
       <c r="G35">
         <v>107.3</v>
@@ -4282,37 +4282,37 @@
         <v>213.4</v>
       </c>
       <c r="M35">
-        <v>237.4776426000001</v>
+        <v>244.6739348000001</v>
       </c>
       <c r="N35">
-        <v>-24.07764260000005</v>
+        <v>-31.27393480000006</v>
       </c>
       <c r="O35">
-        <v>-3.515335819600007</v>
+        <v>-4.565994480800009</v>
       </c>
       <c r="P35">
-        <v>-20.56230678040004</v>
+        <v>-26.70794031920006</v>
       </c>
       <c r="Q35">
-        <v>4.437693219599961</v>
+        <v>-1.707940319200056</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1248332894859397</v>
+        <v>0.12603076356906</v>
       </c>
       <c r="T35">
-        <v>1.825249179813851</v>
+        <v>1.852904470417091</v>
       </c>
       <c r="U35">
         <v>0.1186</v>
       </c>
       <c r="V35">
-        <v>0.1311971925394209</v>
+        <v>0.1273384515823791</v>
       </c>
       <c r="W35">
-        <v>0.1030400129648247</v>
+        <v>0.1034976596423298</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.898610907804253</v>
+        <v>0.872181175221775</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1183695082339718</v>
+        <v>0.1190975082339718</v>
       </c>
       <c r="C36">
-        <v>2508.691897208617</v>
+        <v>2403.673820909088</v>
       </c>
       <c r="D36">
-        <v>4464.409897208618</v>
+        <v>4420.068820909089</v>
       </c>
       <c r="E36">
-        <v>1157.418000000001</v>
+        <v>1218.095000000001</v>
       </c>
       <c r="F36">
-        <v>2063.018</v>
+        <v>2123.695000000001</v>
       </c>
       <c r="G36">
         <v>107.3</v>
@@ -4364,37 +4364,37 @@
         <v>213.4</v>
       </c>
       <c r="M36">
-        <v>244.6739348000001</v>
+        <v>251.8702270000001</v>
       </c>
       <c r="N36">
-        <v>-31.27393480000006</v>
+        <v>-38.47022700000008</v>
       </c>
       <c r="O36">
-        <v>-4.565994480800009</v>
+        <v>-5.616653142000011</v>
       </c>
       <c r="P36">
-        <v>-26.70794031920006</v>
+        <v>-32.85357385800007</v>
       </c>
       <c r="Q36">
-        <v>-1.707940319200056</v>
+        <v>-7.853573858000068</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.12603076356906</v>
+        <v>0.1272650830085841</v>
       </c>
       <c r="T36">
-        <v>1.852904470417091</v>
+        <v>1.881410693038893</v>
       </c>
       <c r="U36">
         <v>0.1186</v>
       </c>
       <c r="V36">
-        <v>0.1273384515823791</v>
+        <v>0.1237002101085969</v>
       </c>
       <c r="W36">
-        <v>0.1034976596423298</v>
+        <v>0.1039291550811204</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.872181175221775</v>
+        <v>0.8472617130725814</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1190975082339718</v>
+        <v>0.1198255082339718</v>
       </c>
       <c r="C37">
-        <v>2403.673820909088</v>
+        <v>2299.527884614166</v>
       </c>
       <c r="D37">
-        <v>4420.068820909089</v>
+        <v>4376.599884614167</v>
       </c>
       <c r="E37">
-        <v>1218.095000000001</v>
+        <v>1278.772</v>
       </c>
       <c r="F37">
-        <v>2123.695000000001</v>
+        <v>2184.372</v>
       </c>
       <c r="G37">
         <v>107.3</v>
@@ -4446,37 +4446,37 @@
         <v>213.4</v>
       </c>
       <c r="M37">
-        <v>251.8702270000001</v>
+        <v>259.0665192000001</v>
       </c>
       <c r="N37">
-        <v>-38.47022700000008</v>
+        <v>-45.66651920000007</v>
       </c>
       <c r="O37">
-        <v>-5.616653142000011</v>
+        <v>-6.667311803200009</v>
       </c>
       <c r="P37">
-        <v>-32.85357385800007</v>
+        <v>-38.99920739680006</v>
       </c>
       <c r="Q37">
-        <v>-7.853573858000068</v>
+        <v>-13.99920739680006</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1272650830085841</v>
+        <v>0.1285379749305932</v>
       </c>
       <c r="T37">
-        <v>1.881410693038893</v>
+        <v>1.910807735117625</v>
       </c>
       <c r="U37">
         <v>0.1186</v>
       </c>
       <c r="V37">
-        <v>0.1237002101085969</v>
+        <v>0.1202640931611359</v>
       </c>
       <c r="W37">
-        <v>0.1039291550811204</v>
+        <v>0.1043366785510893</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8472617130725814</v>
+        <v>0.8237266654872319</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1198255082339718</v>
+        <v>0.1205535082339718</v>
       </c>
       <c r="C38">
-        <v>2299.527884614165</v>
+        <v>2196.228607863933</v>
       </c>
       <c r="D38">
-        <v>4376.599884614166</v>
+        <v>4333.977607863933</v>
       </c>
       <c r="E38">
-        <v>1278.772</v>
+        <v>1339.449000000001</v>
       </c>
       <c r="F38">
-        <v>2184.372</v>
+        <v>2245.049</v>
       </c>
       <c r="G38">
         <v>107.3</v>
@@ -4528,37 +4528,37 @@
         <v>213.4</v>
       </c>
       <c r="M38">
-        <v>259.0665192000001</v>
+        <v>266.2628114000001</v>
       </c>
       <c r="N38">
-        <v>-45.66651920000007</v>
+        <v>-52.86281140000008</v>
       </c>
       <c r="O38">
-        <v>-6.667311803200009</v>
+        <v>-7.717970464400012</v>
       </c>
       <c r="P38">
-        <v>-38.99920739680006</v>
+        <v>-45.14484093560007</v>
       </c>
       <c r="Q38">
-        <v>-13.99920739680006</v>
+        <v>-20.14484093560007</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1285379749305932</v>
+        <v>0.1298512761199677</v>
       </c>
       <c r="T38">
-        <v>1.910807735117625</v>
+        <v>1.941138016627429</v>
       </c>
       <c r="U38">
         <v>0.1186</v>
       </c>
       <c r="V38">
-        <v>0.1202640931611359</v>
+        <v>0.1170137122648889</v>
       </c>
       <c r="W38">
-        <v>0.1043366785510893</v>
+        <v>0.1047221737253842</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8237266654872319</v>
+        <v>0.8014637826362256</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1205535082339718</v>
+        <v>0.1534984730735995</v>
       </c>
       <c r="C39">
-        <v>2196.228607863933</v>
+        <v>809.7877800960523</v>
       </c>
       <c r="D39">
-        <v>4333.977607863933</v>
+        <v>3008.213780096052</v>
       </c>
       <c r="E39">
-        <v>1339.449000000001</v>
+        <v>1400.126</v>
       </c>
       <c r="F39">
-        <v>2245.049</v>
+        <v>2305.726</v>
       </c>
       <c r="G39">
         <v>107.3</v>
@@ -4610,45 +4610,45 @@
         <v>213.4</v>
       </c>
       <c r="M39">
-        <v>266.2628114000001</v>
+        <v>462.9897808000001</v>
       </c>
       <c r="N39">
-        <v>-52.86281140000008</v>
+        <v>-249.5897808000001</v>
       </c>
       <c r="O39">
-        <v>-7.717970464400012</v>
+        <v>-36.44010799680001</v>
       </c>
       <c r="P39">
-        <v>-45.14484093560007</v>
+        <v>-213.1496728032</v>
       </c>
       <c r="Q39">
-        <v>-20.14484093560007</v>
+        <v>-188.1496728032</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1298512761199677</v>
+        <v>0.1327891432180765</v>
       </c>
       <c r="T39">
-        <v>1.941138016627429</v>
+        <v>2.008987141295069</v>
       </c>
       <c r="U39">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1170137122648889</v>
+        <v>0.06729392589651731</v>
       </c>
       <c r="W39">
-        <v>0.1047221737253842</v>
+        <v>0.1872873796799793</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.8014637826362256</v>
+        <v>0.4609173006610775</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1534984730735995</v>
+        <v>0.1550484730735996</v>
       </c>
       <c r="C40">
-        <v>809.7877800960523</v>
+        <v>706.4307203389913</v>
       </c>
       <c r="D40">
-        <v>3008.213780096052</v>
+        <v>2965.533720338991</v>
       </c>
       <c r="E40">
-        <v>1400.126</v>
+        <v>1460.803</v>
       </c>
       <c r="F40">
-        <v>2305.726</v>
+        <v>2366.403</v>
       </c>
       <c r="G40">
         <v>107.3</v>
@@ -4692,37 +4692,37 @@
         <v>213.4</v>
       </c>
       <c r="M40">
-        <v>462.9897808000001</v>
+        <v>475.1737224000001</v>
       </c>
       <c r="N40">
-        <v>-249.5897808000001</v>
+        <v>-261.7737224000001</v>
       </c>
       <c r="O40">
-        <v>-36.44010799680001</v>
+        <v>-38.21896347040001</v>
       </c>
       <c r="P40">
-        <v>-213.1496728032</v>
+        <v>-223.5547589296001</v>
       </c>
       <c r="Q40">
-        <v>-188.1496728032</v>
+        <v>-198.5547589296001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1327891432180765</v>
+        <v>0.1342151947462417</v>
       </c>
       <c r="T40">
-        <v>2.008987141295069</v>
+        <v>2.041921356726136</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.06729392589651731</v>
+        <v>0.06556844061711943</v>
       </c>
       <c r="W40">
-        <v>0.1872873796799793</v>
+        <v>0.1876338571240824</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4609173006610775</v>
+        <v>0.4490989083364344</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1550484730735996</v>
+        <v>0.1565984730735995</v>
       </c>
       <c r="C41">
-        <v>706.4307203389913</v>
+        <v>604.2677942335654</v>
       </c>
       <c r="D41">
-        <v>2965.533720338991</v>
+        <v>2924.047794233566</v>
       </c>
       <c r="E41">
-        <v>1460.803</v>
+        <v>1521.48</v>
       </c>
       <c r="F41">
-        <v>2366.403</v>
+        <v>2427.08</v>
       </c>
       <c r="G41">
         <v>107.3</v>
@@ -4774,37 +4774,37 @@
         <v>213.4</v>
       </c>
       <c r="M41">
-        <v>475.1737224000001</v>
+        <v>487.3576640000001</v>
       </c>
       <c r="N41">
-        <v>-261.7737224000001</v>
+        <v>-273.9576640000001</v>
       </c>
       <c r="O41">
-        <v>-38.21896347040001</v>
+        <v>-39.99781894400002</v>
       </c>
       <c r="P41">
-        <v>-223.5547589296001</v>
+        <v>-233.9598450560001</v>
       </c>
       <c r="Q41">
-        <v>-198.5547589296001</v>
+        <v>-208.9598450560001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1342151947462417</v>
+        <v>0.1356887813253457</v>
       </c>
       <c r="T41">
-        <v>2.041921356726136</v>
+        <v>2.075953379338237</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.06556844061711943</v>
+        <v>0.06392922960169144</v>
       </c>
       <c r="W41">
-        <v>0.1876338571240824</v>
+        <v>0.1879630106959804</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4490989083364344</v>
+        <v>0.4378714356280236</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1565984730735995</v>
+        <v>0.1581484730735996</v>
       </c>
       <c r="C42">
-        <v>604.2677942335654</v>
+        <v>503.249577685895</v>
       </c>
       <c r="D42">
-        <v>2924.047794233566</v>
+        <v>2883.706577685895</v>
       </c>
       <c r="E42">
-        <v>1521.48</v>
+        <v>1582.157000000001</v>
       </c>
       <c r="F42">
-        <v>2427.08</v>
+        <v>2487.757000000001</v>
       </c>
       <c r="G42">
         <v>107.3</v>
@@ -4856,37 +4856,37 @@
         <v>213.4</v>
       </c>
       <c r="M42">
-        <v>487.3576640000001</v>
+        <v>499.5416056000001</v>
       </c>
       <c r="N42">
-        <v>-273.9576640000001</v>
+        <v>-286.1416056000002</v>
       </c>
       <c r="O42">
-        <v>-39.99781894400002</v>
+        <v>-41.77667441760002</v>
       </c>
       <c r="P42">
-        <v>-233.9598450560001</v>
+        <v>-244.3649311824001</v>
       </c>
       <c r="Q42">
-        <v>-208.9598450560001</v>
+        <v>-219.3649311824001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1356887813253457</v>
+        <v>0.137212319991877</v>
       </c>
       <c r="T42">
-        <v>2.075953379338237</v>
+        <v>2.111139029835496</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.06392922960169144</v>
+        <v>0.06236998009921116</v>
       </c>
       <c r="W42">
-        <v>0.1879630106959804</v>
+        <v>0.1882761079960784</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4378714356280236</v>
+        <v>0.4271916445151449</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1581484730735996</v>
+        <v>0.1596984730735996</v>
       </c>
       <c r="C43">
-        <v>503.249577685895</v>
+        <v>403.3293369751541</v>
       </c>
       <c r="D43">
-        <v>2883.706577685895</v>
+        <v>2844.463336975155</v>
       </c>
       <c r="E43">
-        <v>1582.157000000001</v>
+        <v>1642.834000000001</v>
       </c>
       <c r="F43">
-        <v>2487.757000000001</v>
+        <v>2548.434000000001</v>
       </c>
       <c r="G43">
         <v>107.3</v>
@@ -4938,37 +4938,37 @@
         <v>213.4</v>
       </c>
       <c r="M43">
-        <v>499.5416056000001</v>
+        <v>511.7255472000002</v>
       </c>
       <c r="N43">
-        <v>-286.1416056000002</v>
+        <v>-298.3255472000002</v>
       </c>
       <c r="O43">
-        <v>-41.77667441760002</v>
+        <v>-43.55552989120002</v>
       </c>
       <c r="P43">
-        <v>-244.3649311824001</v>
+        <v>-254.7700173088002</v>
       </c>
       <c r="Q43">
-        <v>-219.3649311824001</v>
+        <v>-229.7700173088002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.137212319991877</v>
+        <v>0.1387883944744955</v>
       </c>
       <c r="T43">
-        <v>2.111139029835496</v>
+        <v>2.147537978625763</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.06236998009921116</v>
+        <v>0.06088498057303946</v>
       </c>
       <c r="W43">
-        <v>0.1882761079960784</v>
+        <v>0.1885742959009337</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4271916445151449</v>
+        <v>0.4170204148838319</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1596984730735996</v>
+        <v>0.1612484730735996</v>
       </c>
       <c r="C44">
-        <v>403.3293369751545</v>
+        <v>304.4628481501204</v>
       </c>
       <c r="D44">
-        <v>2844.463336975155</v>
+        <v>2806.273848150121</v>
       </c>
       <c r="E44">
-        <v>1642.834</v>
+        <v>1703.511</v>
       </c>
       <c r="F44">
-        <v>2548.434</v>
+        <v>2609.111</v>
       </c>
       <c r="G44">
         <v>107.3</v>
@@ -5020,37 +5020,37 @@
         <v>213.4</v>
       </c>
       <c r="M44">
-        <v>511.7255472000001</v>
+        <v>523.9094888000001</v>
       </c>
       <c r="N44">
-        <v>-298.3255472000001</v>
+        <v>-310.5094888000001</v>
       </c>
       <c r="O44">
-        <v>-43.55552989120001</v>
+        <v>-45.33438536480001</v>
       </c>
       <c r="P44">
-        <v>-254.7700173088</v>
+        <v>-265.1751034352001</v>
       </c>
       <c r="Q44">
-        <v>-229.7700173088</v>
+        <v>-240.1751034352001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1387883944744955</v>
+        <v>0.1404197698161533</v>
       </c>
       <c r="T44">
-        <v>2.147537978625763</v>
+        <v>2.185214083513934</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.06088498057303948</v>
+        <v>0.05946905079227112</v>
       </c>
       <c r="W44">
-        <v>0.1885742959009337</v>
+        <v>0.188858614600912</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.417020414883832</v>
+        <v>0.407322265700487</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1612484730735996</v>
+        <v>0.1627984730735996</v>
       </c>
       <c r="C45">
-        <v>304.4628481501204</v>
+        <v>206.6082307815886</v>
       </c>
       <c r="D45">
-        <v>2806.273848150121</v>
+        <v>2769.096230781589</v>
       </c>
       <c r="E45">
-        <v>1703.511</v>
+        <v>1764.188000000001</v>
       </c>
       <c r="F45">
-        <v>2609.111</v>
+        <v>2669.788</v>
       </c>
       <c r="G45">
         <v>107.3</v>
@@ -5102,37 +5102,37 @@
         <v>213.4</v>
       </c>
       <c r="M45">
-        <v>523.9094888000001</v>
+        <v>536.0934304000001</v>
       </c>
       <c r="N45">
-        <v>-310.5094888000001</v>
+        <v>-322.6934304000001</v>
       </c>
       <c r="O45">
-        <v>-45.33438536480001</v>
+        <v>-47.11324083840002</v>
       </c>
       <c r="P45">
-        <v>-265.1751034352001</v>
+        <v>-275.5801895616001</v>
       </c>
       <c r="Q45">
-        <v>-240.1751034352001</v>
+        <v>-250.5801895616001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1404197698161533</v>
+        <v>0.1421094085628704</v>
       </c>
       <c r="T45">
-        <v>2.185214083513934</v>
+        <v>2.224235763576683</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.05946905079227112</v>
+        <v>0.05811748145608313</v>
       </c>
       <c r="W45">
-        <v>0.188858614600912</v>
+        <v>0.1891300097236185</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.407322265700487</v>
+        <v>0.3980649414800215</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1627984730735996</v>
+        <v>0.1643484730735996</v>
       </c>
       <c r="C46">
-        <v>206.6082307815886</v>
+        <v>109.7257947567255</v>
       </c>
       <c r="D46">
-        <v>2769.096230781589</v>
+        <v>2732.890794756726</v>
       </c>
       <c r="E46">
-        <v>1764.188000000001</v>
+        <v>1824.865000000001</v>
       </c>
       <c r="F46">
-        <v>2669.788</v>
+        <v>2730.465000000001</v>
       </c>
       <c r="G46">
         <v>107.3</v>
@@ -5184,37 +5184,37 @@
         <v>213.4</v>
       </c>
       <c r="M46">
-        <v>536.0934304000001</v>
+        <v>548.2773720000001</v>
       </c>
       <c r="N46">
-        <v>-322.6934304000001</v>
+        <v>-334.8773720000002</v>
       </c>
       <c r="O46">
-        <v>-47.11324083840002</v>
+        <v>-48.89209631200002</v>
       </c>
       <c r="P46">
-        <v>-275.5801895616001</v>
+        <v>-285.9852756880001</v>
       </c>
       <c r="Q46">
-        <v>-250.5801895616001</v>
+        <v>-260.9852756880001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1421094085628704</v>
+        <v>0.1438604887185589</v>
       </c>
       <c r="T46">
-        <v>2.224235763576683</v>
+        <v>2.264676413823532</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.05811748145608313</v>
+        <v>0.05682598186817017</v>
       </c>
       <c r="W46">
-        <v>0.1891300097236185</v>
+        <v>0.1893893428408714</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3980649414800215</v>
+        <v>0.3892190538915765</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1643484730735996</v>
+        <v>0.1658984730735996</v>
       </c>
       <c r="C47">
-        <v>109.7257947567255</v>
+        <v>13.77789893711815</v>
       </c>
       <c r="D47">
-        <v>2732.890794756726</v>
+        <v>2697.619898937118</v>
       </c>
       <c r="E47">
-        <v>1824.865000000001</v>
+        <v>1885.542</v>
       </c>
       <c r="F47">
-        <v>2730.465000000001</v>
+        <v>2791.142</v>
       </c>
       <c r="G47">
         <v>107.3</v>
@@ -5266,37 +5266,37 @@
         <v>213.4</v>
       </c>
       <c r="M47">
-        <v>548.2773720000001</v>
+        <v>560.4613136</v>
       </c>
       <c r="N47">
-        <v>-334.8773720000002</v>
+        <v>-347.0613136000001</v>
       </c>
       <c r="O47">
-        <v>-48.89209631200002</v>
+        <v>-50.6709517856</v>
       </c>
       <c r="P47">
-        <v>-285.9852756880001</v>
+        <v>-296.3903618144001</v>
       </c>
       <c r="Q47">
-        <v>-260.9852756880001</v>
+        <v>-271.3903618144001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1438604887185589</v>
+        <v>0.1456764236948285</v>
       </c>
       <c r="T47">
-        <v>2.264676413823532</v>
+        <v>2.306614865931375</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.05682598186817017</v>
+        <v>0.05559063443625344</v>
       </c>
       <c r="W47">
-        <v>0.1893893428408714</v>
+        <v>0.1896374006052003</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3892190538915765</v>
+        <v>0.3807577701113248</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1658984730735996</v>
+        <v>0.1674484730735996</v>
       </c>
       <c r="C48">
-        <v>13.77789893711815</v>
+        <v>-81.2711793776075</v>
       </c>
       <c r="D48">
-        <v>2697.619898937118</v>
+        <v>2663.247820622393</v>
       </c>
       <c r="E48">
-        <v>1885.542</v>
+        <v>1946.219000000001</v>
       </c>
       <c r="F48">
-        <v>2791.142</v>
+        <v>2851.819</v>
       </c>
       <c r="G48">
         <v>107.3</v>
@@ -5348,37 +5348,37 @@
         <v>213.4</v>
       </c>
       <c r="M48">
-        <v>560.4613136</v>
+        <v>572.6452552000001</v>
       </c>
       <c r="N48">
-        <v>-347.0613136000001</v>
+        <v>-359.2452552000001</v>
       </c>
       <c r="O48">
-        <v>-50.6709517856</v>
+        <v>-52.44980725920001</v>
       </c>
       <c r="P48">
-        <v>-296.3903618144001</v>
+        <v>-306.7954479408001</v>
       </c>
       <c r="Q48">
-        <v>-271.3903618144001</v>
+        <v>-281.7954479408001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1456764236948285</v>
+        <v>0.1475608845192592</v>
       </c>
       <c r="T48">
-        <v>2.306614865931375</v>
+        <v>2.350135901137627</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.05559063443625344</v>
+        <v>0.05440785498016294</v>
       </c>
       <c r="W48">
-        <v>0.1896374006052003</v>
+        <v>0.1898749027199833</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3807577701113248</v>
+        <v>0.3726565409600201</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1674484730735996</v>
+        <v>0.1689984730735996</v>
       </c>
       <c r="C49">
-        <v>-81.2711793776075</v>
+        <v>-175.4553651322444</v>
       </c>
       <c r="D49">
-        <v>2663.247820622393</v>
+        <v>2629.740634867756</v>
       </c>
       <c r="E49">
-        <v>1946.219000000001</v>
+        <v>2006.896000000001</v>
       </c>
       <c r="F49">
-        <v>2851.819</v>
+        <v>2912.496000000001</v>
       </c>
       <c r="G49">
         <v>107.3</v>
@@ -5430,37 +5430,37 @@
         <v>213.4</v>
       </c>
       <c r="M49">
-        <v>572.6452552000001</v>
+        <v>584.8291968000001</v>
       </c>
       <c r="N49">
-        <v>-359.2452552000001</v>
+        <v>-371.4291968000001</v>
       </c>
       <c r="O49">
-        <v>-52.44980725920001</v>
+        <v>-54.22866273280001</v>
       </c>
       <c r="P49">
-        <v>-306.7954479408001</v>
+        <v>-317.2005340672001</v>
       </c>
       <c r="Q49">
-        <v>-281.7954479408001</v>
+        <v>-292.2005340672001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1475608845192592</v>
+        <v>0.1495178246061681</v>
       </c>
       <c r="T49">
-        <v>2.350135901137627</v>
+        <v>2.395330822313351</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.05440785498016294</v>
+        <v>0.05327435800140954</v>
       </c>
       <c r="W49">
-        <v>0.1898749027199833</v>
+        <v>0.190102508913317</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3726565409600201</v>
+        <v>0.364892863023353</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1689984730735996</v>
+        <v>0.1705484730735995</v>
       </c>
       <c r="C50">
-        <v>-175.455365132244</v>
+        <v>-268.8068972015876</v>
       </c>
       <c r="D50">
-        <v>2629.740634867756</v>
+        <v>2597.066102798412</v>
       </c>
       <c r="E50">
-        <v>2006.896</v>
+        <v>2067.573</v>
       </c>
       <c r="F50">
-        <v>2912.496</v>
+        <v>2973.173</v>
       </c>
       <c r="G50">
         <v>107.3</v>
@@ -5512,37 +5512,37 @@
         <v>213.4</v>
       </c>
       <c r="M50">
-        <v>584.8291968000001</v>
+        <v>597.0131384000001</v>
       </c>
       <c r="N50">
-        <v>-371.4291968000001</v>
+        <v>-383.6131384000001</v>
       </c>
       <c r="O50">
-        <v>-54.22866273280001</v>
+        <v>-56.00751820640001</v>
       </c>
       <c r="P50">
-        <v>-317.2005340672001</v>
+        <v>-327.6056201936001</v>
       </c>
       <c r="Q50">
-        <v>-292.2005340672001</v>
+        <v>-302.6056201936001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1495178246061681</v>
+        <v>0.1515515074415831</v>
       </c>
       <c r="T50">
-        <v>2.395330822313351</v>
+        <v>2.442298093339103</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.05327435800140954</v>
+        <v>0.0521871262054624</v>
       </c>
       <c r="W50">
-        <v>0.190102508913317</v>
+        <v>0.1903208250579431</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.364892863023353</v>
+        <v>0.3574460699004274</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1705484730735995</v>
+        <v>0.1720984730735995</v>
       </c>
       <c r="C51">
-        <v>-268.8068972015876</v>
+        <v>-361.3564318520407</v>
       </c>
       <c r="D51">
-        <v>2597.066102798412</v>
+        <v>2565.193568147959</v>
       </c>
       <c r="E51">
-        <v>2067.573</v>
+        <v>2128.25</v>
       </c>
       <c r="F51">
-        <v>2973.173</v>
+        <v>3033.85</v>
       </c>
       <c r="G51">
         <v>107.3</v>
@@ -5594,37 +5594,37 @@
         <v>213.4</v>
       </c>
       <c r="M51">
-        <v>597.0131384000001</v>
+        <v>609.1970800000001</v>
       </c>
       <c r="N51">
-        <v>-383.6131384000001</v>
+        <v>-395.7970800000002</v>
       </c>
       <c r="O51">
-        <v>-56.00751820640001</v>
+        <v>-57.78637368000002</v>
       </c>
       <c r="P51">
-        <v>-327.6056201936001</v>
+        <v>-338.0107063200002</v>
       </c>
       <c r="Q51">
-        <v>-302.6056201936001</v>
+        <v>-313.0107063200002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1515515074415831</v>
+        <v>0.1536665375904148</v>
       </c>
       <c r="T51">
-        <v>2.442298093339103</v>
+        <v>2.491144055205885</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.0521871262054624</v>
+        <v>0.05114338368135316</v>
       </c>
       <c r="W51">
-        <v>0.1903208250579431</v>
+        <v>0.1905304085567843</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3574460699004274</v>
+        <v>0.3502971485024189</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1720984730735995</v>
+        <v>0.1736484730735995</v>
       </c>
       <c r="C52">
-        <v>-361.3564318520407</v>
+        <v>-453.1331386771694</v>
       </c>
       <c r="D52">
-        <v>2565.193568147959</v>
+        <v>2534.093861322831</v>
       </c>
       <c r="E52">
-        <v>2128.25</v>
+        <v>2188.927000000001</v>
       </c>
       <c r="F52">
-        <v>3033.85</v>
+        <v>3094.527</v>
       </c>
       <c r="G52">
         <v>107.3</v>
@@ -5676,37 +5676,37 @@
         <v>213.4</v>
       </c>
       <c r="M52">
-        <v>609.1970800000001</v>
+        <v>621.3810216000002</v>
       </c>
       <c r="N52">
-        <v>-395.7970800000002</v>
+        <v>-407.9810216000002</v>
       </c>
       <c r="O52">
-        <v>-57.78637368000002</v>
+        <v>-59.56522915360002</v>
       </c>
       <c r="P52">
-        <v>-338.0107063200002</v>
+        <v>-348.4157924464002</v>
       </c>
       <c r="Q52">
-        <v>-313.0107063200002</v>
+        <v>-323.4157924464002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1536665375904148</v>
+        <v>0.1558678955004233</v>
       </c>
       <c r="T52">
-        <v>2.491144055205885</v>
+        <v>2.541983729801923</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.05114338368135316</v>
+        <v>0.05014057223662074</v>
       </c>
       <c r="W52">
-        <v>0.1905304085567843</v>
+        <v>0.1907317730948866</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3502971485024189</v>
+        <v>0.3434285769631558</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1736484730735995</v>
+        <v>0.1751984730735995</v>
       </c>
       <c r="C53">
-        <v>-453.1331386771694</v>
+        <v>-544.1647896382851</v>
       </c>
       <c r="D53">
-        <v>2534.093861322831</v>
+        <v>2503.739210361715</v>
       </c>
       <c r="E53">
-        <v>2188.927000000001</v>
+        <v>2249.604000000001</v>
       </c>
       <c r="F53">
-        <v>3094.527</v>
+        <v>3155.204000000001</v>
       </c>
       <c r="G53">
         <v>107.3</v>
@@ -5758,37 +5758,37 @@
         <v>213.4</v>
       </c>
       <c r="M53">
-        <v>621.3810216000002</v>
+        <v>633.5649632000002</v>
       </c>
       <c r="N53">
-        <v>-407.9810216000002</v>
+        <v>-420.1649632000002</v>
       </c>
       <c r="O53">
-        <v>-59.56522915360002</v>
+        <v>-61.34408462720003</v>
       </c>
       <c r="P53">
-        <v>-348.4157924464002</v>
+        <v>-358.8208785728002</v>
       </c>
       <c r="Q53">
-        <v>-323.4157924464002</v>
+        <v>-333.8208785728002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1558678955004233</v>
+        <v>0.1581609766566821</v>
       </c>
       <c r="T53">
-        <v>2.541983729801923</v>
+        <v>2.594941724172797</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.05014057223662074</v>
+        <v>0.04917633046283957</v>
       </c>
       <c r="W53">
-        <v>0.1907317730948866</v>
+        <v>0.1909253928430618</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3434285769631558</v>
+        <v>0.3368241812523258</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1751984730735995</v>
+        <v>0.1767484730735996</v>
       </c>
       <c r="C54">
-        <v>-544.1647896382851</v>
+        <v>-634.4778417813254</v>
       </c>
       <c r="D54">
-        <v>2503.739210361715</v>
+        <v>2474.103158218675</v>
       </c>
       <c r="E54">
-        <v>2249.604000000001</v>
+        <v>2310.281000000001</v>
       </c>
       <c r="F54">
-        <v>3155.204000000001</v>
+        <v>3215.881000000001</v>
       </c>
       <c r="G54">
         <v>107.3</v>
@@ -5840,37 +5840,37 @@
         <v>213.4</v>
       </c>
       <c r="M54">
-        <v>633.5649632000002</v>
+        <v>645.7489048000002</v>
       </c>
       <c r="N54">
-        <v>-420.1649632000002</v>
+        <v>-432.3489048000002</v>
       </c>
       <c r="O54">
-        <v>-61.34408462720003</v>
+        <v>-63.12294010080003</v>
       </c>
       <c r="P54">
-        <v>-358.8208785728002</v>
+        <v>-369.2259646992002</v>
       </c>
       <c r="Q54">
-        <v>-333.8208785728002</v>
+        <v>-344.2259646992002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1581609766566821</v>
+        <v>0.1605516357344839</v>
       </c>
       <c r="T54">
-        <v>2.594941724172797</v>
+        <v>2.650153250219027</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.04917633046283957</v>
+        <v>0.04824847517108788</v>
       </c>
       <c r="W54">
-        <v>0.1909253928430618</v>
+        <v>0.1911117061856455</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3368241812523258</v>
+        <v>0.3304690080211498</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1767484730735996</v>
+        <v>0.1782984730735996</v>
       </c>
       <c r="C55">
-        <v>-634.4778417813254</v>
+        <v>-724.0975141478871</v>
       </c>
       <c r="D55">
-        <v>2474.103158218675</v>
+        <v>2445.160485852113</v>
       </c>
       <c r="E55">
-        <v>2310.281000000001</v>
+        <v>2370.958000000001</v>
       </c>
       <c r="F55">
-        <v>3215.881000000001</v>
+        <v>3276.558</v>
       </c>
       <c r="G55">
         <v>107.3</v>
@@ -5922,37 +5922,37 @@
         <v>213.4</v>
       </c>
       <c r="M55">
-        <v>645.7489048000002</v>
+        <v>657.9328464000001</v>
       </c>
       <c r="N55">
-        <v>-432.3489048000002</v>
+        <v>-444.5328464000002</v>
       </c>
       <c r="O55">
-        <v>-63.12294010080003</v>
+        <v>-64.90179557440001</v>
       </c>
       <c r="P55">
-        <v>-369.2259646992002</v>
+        <v>-379.6310508256001</v>
       </c>
       <c r="Q55">
-        <v>-344.2259646992002</v>
+        <v>-354.6310508256001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1605516357344839</v>
+        <v>0.1630462365113204</v>
       </c>
       <c r="T55">
-        <v>2.650153250219027</v>
+        <v>2.707765277397701</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.04824847517108788</v>
+        <v>0.04735498489014181</v>
       </c>
       <c r="W55">
-        <v>0.1911117061856455</v>
+        <v>0.1912911190340595</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3304690080211498</v>
+        <v>0.3243492115763138</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1782984730735996</v>
+        <v>0.1798484730735996</v>
       </c>
       <c r="C56">
-        <v>-724.0975141478871</v>
+        <v>-813.0478593503349</v>
       </c>
       <c r="D56">
-        <v>2445.160485852113</v>
+        <v>2416.887140649666</v>
       </c>
       <c r="E56">
-        <v>2370.958000000001</v>
+        <v>2431.635000000001</v>
       </c>
       <c r="F56">
-        <v>3276.558</v>
+        <v>3337.235000000001</v>
       </c>
       <c r="G56">
         <v>107.3</v>
@@ -6004,37 +6004,37 @@
         <v>213.4</v>
       </c>
       <c r="M56">
-        <v>657.9328464000001</v>
+        <v>670.1167880000002</v>
       </c>
       <c r="N56">
-        <v>-444.5328464000002</v>
+        <v>-456.7167880000002</v>
       </c>
       <c r="O56">
-        <v>-64.90179557440001</v>
+        <v>-66.68065104800002</v>
       </c>
       <c r="P56">
-        <v>-379.6310508256001</v>
+        <v>-390.0361369520002</v>
       </c>
       <c r="Q56">
-        <v>-354.6310508256001</v>
+        <v>-365.0361369520002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1630462365113204</v>
+        <v>0.1656517084337943</v>
       </c>
       <c r="T56">
-        <v>2.707765277397701</v>
+        <v>2.767937839117651</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.04735498489014181</v>
+        <v>0.0464939851648665</v>
       </c>
       <c r="W56">
-        <v>0.1912911190340595</v>
+        <v>0.1914640077788948</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3243492115763138</v>
+        <v>0.3184519531840171</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1798484730735996</v>
+        <v>0.1813984730735995</v>
       </c>
       <c r="C57">
-        <v>-813.0478593503349</v>
+        <v>-901.3518302379316</v>
       </c>
       <c r="D57">
-        <v>2416.887140649666</v>
+        <v>2389.260169762069</v>
       </c>
       <c r="E57">
-        <v>2431.635000000001</v>
+        <v>2492.312000000001</v>
       </c>
       <c r="F57">
-        <v>3337.235000000001</v>
+        <v>3397.912000000001</v>
       </c>
       <c r="G57">
         <v>107.3</v>
@@ -6086,37 +6086,37 @@
         <v>213.4</v>
       </c>
       <c r="M57">
-        <v>670.1167880000002</v>
+        <v>682.3007296000002</v>
       </c>
       <c r="N57">
-        <v>-456.7167880000002</v>
+        <v>-468.9007296000002</v>
       </c>
       <c r="O57">
-        <v>-66.68065104800002</v>
+        <v>-68.45950652160002</v>
       </c>
       <c r="P57">
-        <v>-390.0361369520002</v>
+        <v>-400.4412230784002</v>
       </c>
       <c r="Q57">
-        <v>-365.0361369520002</v>
+        <v>-375.4412230784002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1656517084337943</v>
+        <v>0.1683756108981986</v>
       </c>
       <c r="T57">
-        <v>2.767937839117651</v>
+        <v>2.830845517279415</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.0464939851648665</v>
+        <v>0.0456637354297796</v>
       </c>
       <c r="W57">
-        <v>0.1914640077788948</v>
+        <v>0.1916307219257002</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3184519531840171</v>
+        <v>0.312765311162874</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1813984730735995</v>
+        <v>0.1829484730735996</v>
       </c>
       <c r="C58">
-        <v>-901.3518302379316</v>
+        <v>-989.0313420423754</v>
       </c>
       <c r="D58">
-        <v>2389.260169762069</v>
+        <v>2362.257657957625</v>
       </c>
       <c r="E58">
-        <v>2492.312000000001</v>
+        <v>2552.989000000001</v>
       </c>
       <c r="F58">
-        <v>3397.912000000001</v>
+        <v>3458.589000000001</v>
       </c>
       <c r="G58">
         <v>107.3</v>
@@ -6168,37 +6168,37 @@
         <v>213.4</v>
       </c>
       <c r="M58">
-        <v>682.3007296000002</v>
+        <v>694.4846712000002</v>
       </c>
       <c r="N58">
-        <v>-468.9007296000002</v>
+        <v>-481.0846712000002</v>
       </c>
       <c r="O58">
-        <v>-68.45950652160002</v>
+        <v>-70.23836199520002</v>
       </c>
       <c r="P58">
-        <v>-400.4412230784002</v>
+        <v>-410.8463092048002</v>
       </c>
       <c r="Q58">
-        <v>-375.4412230784002</v>
+        <v>-385.8463092048002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1683756108981986</v>
+        <v>0.1712262065004823</v>
       </c>
       <c r="T58">
-        <v>2.830845517279415</v>
+        <v>2.896679133960332</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.0456637354297796</v>
+        <v>0.04486261726434487</v>
       </c>
       <c r="W58">
-        <v>0.1916307219257002</v>
+        <v>0.1917915864533196</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.312765311162874</v>
+        <v>0.3072782004407183</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1829484730735996</v>
+        <v>0.1844984730735996</v>
       </c>
       <c r="C59">
-        <v>-989.0313420423754</v>
+        <v>-1076.107330356337</v>
       </c>
       <c r="D59">
-        <v>2362.257657957625</v>
+        <v>2335.858669643664</v>
       </c>
       <c r="E59">
-        <v>2552.989000000001</v>
+        <v>2613.666000000001</v>
       </c>
       <c r="F59">
-        <v>3458.589000000001</v>
+        <v>3519.266000000001</v>
       </c>
       <c r="G59">
         <v>107.3</v>
@@ -6250,37 +6250,37 @@
         <v>213.4</v>
       </c>
       <c r="M59">
-        <v>694.4846712000002</v>
+        <v>706.6686128000002</v>
       </c>
       <c r="N59">
-        <v>-481.0846712000002</v>
+        <v>-493.2686128000003</v>
       </c>
       <c r="O59">
-        <v>-70.23836199520002</v>
+        <v>-72.01721746880003</v>
       </c>
       <c r="P59">
-        <v>-410.8463092048002</v>
+        <v>-421.2513953312002</v>
       </c>
       <c r="Q59">
-        <v>-385.8463092048002</v>
+        <v>-396.2513953312002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1712262065004823</v>
+        <v>0.1742125447504939</v>
       </c>
       <c r="T59">
-        <v>2.896679133960332</v>
+        <v>2.965647684768911</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.04486261726434487</v>
+        <v>0.04408912386323547</v>
       </c>
       <c r="W59">
-        <v>0.1917915864533196</v>
+        <v>0.1919469039282623</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3072782004407183</v>
+        <v>0.3019803004331196</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1844984730735996</v>
+        <v>0.1860484730735996</v>
       </c>
       <c r="C60">
-        <v>-1076.107330356336</v>
+        <v>-1162.599805267408</v>
       </c>
       <c r="D60">
-        <v>2335.858669643664</v>
+        <v>2310.043194732592</v>
       </c>
       <c r="E60">
-        <v>2613.666</v>
+        <v>2674.343</v>
       </c>
       <c r="F60">
-        <v>3519.266</v>
+        <v>3579.943</v>
       </c>
       <c r="G60">
         <v>107.3</v>
@@ -6332,37 +6332,37 @@
         <v>213.4</v>
       </c>
       <c r="M60">
-        <v>706.6686128</v>
+        <v>718.8525544</v>
       </c>
       <c r="N60">
-        <v>-493.2686128</v>
+        <v>-505.4525544000001</v>
       </c>
       <c r="O60">
-        <v>-72.0172174688</v>
+        <v>-73.7960729424</v>
       </c>
       <c r="P60">
-        <v>-421.2513953312</v>
+        <v>-431.6564814576001</v>
       </c>
       <c r="Q60">
-        <v>-396.2513953312</v>
+        <v>-406.6564814576001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1742125447504938</v>
+        <v>0.1773445580370912</v>
       </c>
       <c r="T60">
-        <v>2.965647684768911</v>
+        <v>3.037980555129128</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.04408912386323549</v>
+        <v>0.04334185057741793</v>
       </c>
       <c r="W60">
-        <v>0.1919469039282623</v>
+        <v>0.1920969564040545</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3019803004331197</v>
+        <v>0.2968619902562872</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1860484730735996</v>
+        <v>0.1875984730735996</v>
       </c>
       <c r="C61">
-        <v>-1162.599805267408</v>
+        <v>-1248.527901941609</v>
       </c>
       <c r="D61">
-        <v>2310.043194732592</v>
+        <v>2284.792098058391</v>
       </c>
       <c r="E61">
-        <v>2674.343</v>
+        <v>2735.02</v>
       </c>
       <c r="F61">
-        <v>3579.943</v>
+        <v>3640.62</v>
       </c>
       <c r="G61">
         <v>107.3</v>
@@ -6414,37 +6414,37 @@
         <v>213.4</v>
       </c>
       <c r="M61">
-        <v>718.8525544</v>
+        <v>731.0364960000001</v>
       </c>
       <c r="N61">
-        <v>-505.4525544000001</v>
+        <v>-517.6364960000001</v>
       </c>
       <c r="O61">
-        <v>-73.7960729424</v>
+        <v>-75.57492841600001</v>
       </c>
       <c r="P61">
-        <v>-431.6564814576001</v>
+        <v>-442.061567584</v>
       </c>
       <c r="Q61">
-        <v>-406.6564814576001</v>
+        <v>-417.061567584</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1773445580370912</v>
+        <v>0.1806331719880185</v>
       </c>
       <c r="T61">
-        <v>3.037980555129128</v>
+        <v>3.113930069007356</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.04334185057741793</v>
+        <v>0.04261948640112764</v>
       </c>
       <c r="W61">
-        <v>0.1920969564040545</v>
+        <v>0.1922420071306536</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2968619902562872</v>
+        <v>0.2919142904186824</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1875984730735996</v>
+        <v>0.1891484730735996</v>
       </c>
       <c r="C62">
-        <v>-1248.527901941609</v>
+        <v>-1333.909927925194</v>
       </c>
       <c r="D62">
-        <v>2284.792098058391</v>
+        <v>2260.087072074807</v>
       </c>
       <c r="E62">
-        <v>2735.02</v>
+        <v>2795.697000000001</v>
       </c>
       <c r="F62">
-        <v>3640.62</v>
+        <v>3701.297</v>
       </c>
       <c r="G62">
         <v>107.3</v>
@@ -6496,37 +6496,37 @@
         <v>213.4</v>
       </c>
       <c r="M62">
-        <v>731.0364960000001</v>
+        <v>743.2204376000001</v>
       </c>
       <c r="N62">
-        <v>-517.6364960000001</v>
+        <v>-529.8204376000001</v>
       </c>
       <c r="O62">
-        <v>-75.57492841600001</v>
+        <v>-77.35378388960001</v>
       </c>
       <c r="P62">
-        <v>-442.061567584</v>
+        <v>-452.4666537104001</v>
       </c>
       <c r="Q62">
-        <v>-417.061567584</v>
+        <v>-427.4666537104001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1806331719880185</v>
+        <v>0.1840904328082241</v>
       </c>
       <c r="T62">
-        <v>3.113930069007356</v>
+        <v>3.193774429751135</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.04261948640112764</v>
+        <v>0.04192080629619112</v>
       </c>
       <c r="W62">
-        <v>0.1922420071306536</v>
+        <v>0.1923823020957248</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2919142904186824</v>
+        <v>0.2871288102478843</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1891484730735996</v>
+        <v>0.1906984730735996</v>
       </c>
       <c r="C63">
-        <v>-1333.909927925194</v>
+        <v>-1418.763407410499</v>
       </c>
       <c r="D63">
-        <v>2260.087072074807</v>
+        <v>2235.910592589501</v>
       </c>
       <c r="E63">
-        <v>2795.697000000001</v>
+        <v>2856.374000000001</v>
       </c>
       <c r="F63">
-        <v>3701.297</v>
+        <v>3761.974000000001</v>
       </c>
       <c r="G63">
         <v>107.3</v>
@@ -6578,37 +6578,37 @@
         <v>213.4</v>
       </c>
       <c r="M63">
-        <v>743.2204376000001</v>
+        <v>755.4043792000001</v>
       </c>
       <c r="N63">
-        <v>-529.8204376000001</v>
+        <v>-542.0043792000001</v>
       </c>
       <c r="O63">
-        <v>-77.35378388960001</v>
+        <v>-79.13263936320001</v>
       </c>
       <c r="P63">
-        <v>-452.4666537104001</v>
+        <v>-462.8717398368001</v>
       </c>
       <c r="Q63">
-        <v>-427.4666537104001</v>
+        <v>-437.8717398368001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1840904328082241</v>
+        <v>0.18772965472423</v>
       </c>
       <c r="T63">
-        <v>3.193774429751135</v>
+        <v>3.277821125270902</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.04192080629619112</v>
+        <v>0.04124466425915577</v>
       </c>
       <c r="W63">
-        <v>0.1923823020957248</v>
+        <v>0.1925180714167615</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2871288102478843</v>
+        <v>0.2824977004051765</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1906984730735996</v>
+        <v>0.1922484730735995</v>
       </c>
       <c r="C64">
-        <v>-1418.763407410499</v>
+        <v>-1503.105122690747</v>
       </c>
       <c r="D64">
-        <v>2235.910592589501</v>
+        <v>2212.245877309254</v>
       </c>
       <c r="E64">
-        <v>2856.374000000001</v>
+        <v>2917.051</v>
       </c>
       <c r="F64">
-        <v>3761.974000000001</v>
+        <v>3822.651</v>
       </c>
       <c r="G64">
         <v>107.3</v>
@@ -6660,37 +6660,37 @@
         <v>213.4</v>
       </c>
       <c r="M64">
-        <v>755.4043792000001</v>
+        <v>767.5883208000001</v>
       </c>
       <c r="N64">
-        <v>-542.0043792000001</v>
+        <v>-554.1883208000002</v>
       </c>
       <c r="O64">
-        <v>-79.13263936320001</v>
+        <v>-80.91149483680002</v>
       </c>
       <c r="P64">
-        <v>-462.8717398368001</v>
+        <v>-473.2768259632002</v>
       </c>
       <c r="Q64">
-        <v>-437.8717398368001</v>
+        <v>-448.2768259632002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.18772965472423</v>
+        <v>0.1915655913383984</v>
       </c>
       <c r="T64">
-        <v>3.277821125270902</v>
+        <v>3.366410885413359</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.04124466425915577</v>
+        <v>0.04058998704869298</v>
       </c>
       <c r="W64">
-        <v>0.1925180714167615</v>
+        <v>0.1926495306006225</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2824977004051765</v>
+        <v>0.2780136099225546</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1922484730735995</v>
+        <v>0.1937984730735995</v>
       </c>
       <c r="C65">
-        <v>-1503.105122690747</v>
+        <v>-1586.951153009891</v>
       </c>
       <c r="D65">
-        <v>2212.245877309254</v>
+        <v>2189.076846990109</v>
       </c>
       <c r="E65">
-        <v>2917.051</v>
+        <v>2977.728000000001</v>
       </c>
       <c r="F65">
-        <v>3822.651</v>
+        <v>3883.328</v>
       </c>
       <c r="G65">
         <v>107.3</v>
@@ -6742,37 +6742,37 @@
         <v>213.4</v>
       </c>
       <c r="M65">
-        <v>767.5883208000001</v>
+        <v>779.7722624000002</v>
       </c>
       <c r="N65">
-        <v>-554.1883208000002</v>
+        <v>-566.3722624000002</v>
       </c>
       <c r="O65">
-        <v>-80.91149483680002</v>
+        <v>-82.69035031040002</v>
       </c>
       <c r="P65">
-        <v>-473.2768259632002</v>
+        <v>-483.6819120896001</v>
       </c>
       <c r="Q65">
-        <v>-448.2768259632002</v>
+        <v>-458.6819120896001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1915655913383984</v>
+        <v>0.1956146355422428</v>
       </c>
       <c r="T65">
-        <v>3.366410885413359</v>
+        <v>3.459922298897062</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.04058998704869298</v>
+        <v>0.03995576850105715</v>
       </c>
       <c r="W65">
-        <v>0.1926495306006225</v>
+        <v>0.1927768816849877</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2780136099225546</v>
+        <v>0.2736696472675147</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1937984730735995</v>
+        <v>0.1953484730735995</v>
       </c>
       <c r="C66">
-        <v>-1586.951153009891</v>
+        <v>-1670.316910996506</v>
       </c>
       <c r="D66">
-        <v>2189.076846990109</v>
+        <v>2166.388089003494</v>
       </c>
       <c r="E66">
-        <v>2977.728000000001</v>
+        <v>3038.405000000001</v>
       </c>
       <c r="F66">
-        <v>3883.328</v>
+        <v>3944.005000000001</v>
       </c>
       <c r="G66">
         <v>107.3</v>
@@ -6824,37 +6824,37 @@
         <v>213.4</v>
       </c>
       <c r="M66">
-        <v>779.7722624000002</v>
+        <v>791.9562040000002</v>
       </c>
       <c r="N66">
-        <v>-566.3722624000002</v>
+        <v>-578.5562040000002</v>
       </c>
       <c r="O66">
-        <v>-82.69035031040002</v>
+        <v>-84.46920578400002</v>
       </c>
       <c r="P66">
-        <v>-483.6819120896001</v>
+        <v>-494.0869982160002</v>
       </c>
       <c r="Q66">
-        <v>-458.6819120896001</v>
+        <v>-469.0869982160002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1956146355422428</v>
+        <v>0.1998950537005926</v>
       </c>
       <c r="T66">
-        <v>3.459922298897062</v>
+        <v>3.558777221722694</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.03995576850105715</v>
+        <v>0.03934106437027166</v>
       </c>
       <c r="W66">
-        <v>0.1927768816849877</v>
+        <v>0.1929003142744495</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2736696472675147</v>
+        <v>0.2694593450018606</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1953484730735995</v>
+        <v>0.1968984730735995</v>
       </c>
       <c r="C67">
-        <v>-1670.316910996506</v>
+        <v>-1753.217176855188</v>
       </c>
       <c r="D67">
-        <v>2166.388089003494</v>
+        <v>2144.164823144813</v>
       </c>
       <c r="E67">
-        <v>3038.405000000001</v>
+        <v>3099.082000000001</v>
       </c>
       <c r="F67">
-        <v>3944.005000000001</v>
+        <v>4004.682000000001</v>
       </c>
       <c r="G67">
         <v>107.3</v>
@@ -6906,37 +6906,37 @@
         <v>213.4</v>
       </c>
       <c r="M67">
-        <v>791.9562040000002</v>
+        <v>804.1401456000002</v>
       </c>
       <c r="N67">
-        <v>-578.5562040000002</v>
+        <v>-590.7401456000002</v>
       </c>
       <c r="O67">
-        <v>-84.46920578400002</v>
+        <v>-86.24806125760003</v>
       </c>
       <c r="P67">
-        <v>-494.0869982160002</v>
+        <v>-504.4920843424002</v>
       </c>
       <c r="Q67">
-        <v>-469.0869982160002</v>
+        <v>-479.4920843424002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1998950537005926</v>
+        <v>0.2044272611623747</v>
       </c>
       <c r="T67">
-        <v>3.558777221722694</v>
+        <v>3.663447140008655</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.03934106437027166</v>
+        <v>0.03874498763738875</v>
       </c>
       <c r="W67">
-        <v>0.1929003142744495</v>
+        <v>0.1930200064824124</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2694593450018606</v>
+        <v>0.2653766276533476</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1968984730735995</v>
+        <v>0.1984484730735995</v>
       </c>
       <c r="C68">
-        <v>-1753.217176855188</v>
+        <v>-1835.666130474875</v>
       </c>
       <c r="D68">
-        <v>2144.164823144813</v>
+        <v>2122.392869525126</v>
       </c>
       <c r="E68">
-        <v>3099.082000000001</v>
+        <v>3159.759000000001</v>
       </c>
       <c r="F68">
-        <v>4004.682000000001</v>
+        <v>4065.359000000001</v>
       </c>
       <c r="G68">
         <v>107.3</v>
@@ -6988,37 +6988,37 @@
         <v>213.4</v>
       </c>
       <c r="M68">
-        <v>804.1401456000002</v>
+        <v>816.3240872000002</v>
       </c>
       <c r="N68">
-        <v>-590.7401456000002</v>
+        <v>-602.9240872000003</v>
       </c>
       <c r="O68">
-        <v>-86.24806125760003</v>
+        <v>-88.02691673120003</v>
       </c>
       <c r="P68">
-        <v>-504.4920843424002</v>
+        <v>-514.8971704688003</v>
       </c>
       <c r="Q68">
-        <v>-479.4920843424002</v>
+        <v>-489.8971704688003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2044272611623747</v>
+        <v>0.2092341478642649</v>
       </c>
       <c r="T68">
-        <v>3.663447140008655</v>
+        <v>3.774460689705887</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.03874498763738875</v>
+        <v>0.03816670423981579</v>
       </c>
       <c r="W68">
-        <v>0.1930200064824124</v>
+        <v>0.193136125788645</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2653766276533476</v>
+        <v>0.2614157824644917</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1984484730735995</v>
+        <v>0.1999984730735996</v>
       </c>
       <c r="C69">
-        <v>-1835.666130474875</v>
+        <v>-1917.677381600655</v>
       </c>
       <c r="D69">
-        <v>2122.392869525126</v>
+        <v>2101.058618399346</v>
       </c>
       <c r="E69">
-        <v>3159.759000000001</v>
+        <v>3220.436000000001</v>
       </c>
       <c r="F69">
-        <v>4065.359000000001</v>
+        <v>4126.036000000001</v>
       </c>
       <c r="G69">
         <v>107.3</v>
@@ -7070,37 +7070,37 @@
         <v>213.4</v>
       </c>
       <c r="M69">
-        <v>816.3240872000002</v>
+        <v>828.5080288000003</v>
       </c>
       <c r="N69">
-        <v>-602.9240872000003</v>
+        <v>-615.1080288000003</v>
       </c>
       <c r="O69">
-        <v>-88.02691673120003</v>
+        <v>-89.80577220480004</v>
       </c>
       <c r="P69">
-        <v>-514.8971704688003</v>
+        <v>-525.3022565952002</v>
       </c>
       <c r="Q69">
-        <v>-489.8971704688003</v>
+        <v>-500.3022565952002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2092341478642649</v>
+        <v>0.2143414649850232</v>
       </c>
       <c r="T69">
-        <v>3.774460689705887</v>
+        <v>3.892412586259196</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.03816670423981579</v>
+        <v>0.03760542917746555</v>
       </c>
       <c r="W69">
-        <v>0.193136125788645</v>
+        <v>0.1932488298211649</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2614157824644917</v>
+        <v>0.2575714327223668</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1999984730735996</v>
+        <v>0.2015484730735996</v>
       </c>
       <c r="C70">
-        <v>-1917.677381600655</v>
+        <v>-1999.263998203959</v>
       </c>
       <c r="D70">
-        <v>2101.058618399346</v>
+        <v>2080.149001796042</v>
       </c>
       <c r="E70">
-        <v>3220.436000000001</v>
+        <v>3281.113000000001</v>
       </c>
       <c r="F70">
-        <v>4126.036000000001</v>
+        <v>4186.713000000001</v>
       </c>
       <c r="G70">
         <v>107.3</v>
@@ -7152,37 +7152,37 @@
         <v>213.4</v>
       </c>
       <c r="M70">
-        <v>828.5080288000003</v>
+        <v>840.6919704000002</v>
       </c>
       <c r="N70">
-        <v>-615.1080288000003</v>
+        <v>-627.2919704000002</v>
       </c>
       <c r="O70">
-        <v>-89.80577220480004</v>
+        <v>-91.58462767840003</v>
       </c>
       <c r="P70">
-        <v>-525.3022565952002</v>
+        <v>-535.7073427216002</v>
       </c>
       <c r="Q70">
-        <v>-500.3022565952002</v>
+        <v>-510.7073427216002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2143414649850232</v>
+        <v>0.219778286436153</v>
       </c>
       <c r="T70">
-        <v>3.892412586259196</v>
+        <v>4.017974282590139</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.03760542917746555</v>
+        <v>0.03706042295750229</v>
       </c>
       <c r="W70">
-        <v>0.1932488298211649</v>
+        <v>0.1933582670701335</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2575714327223668</v>
+        <v>0.2538385134075499</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2015484730735996</v>
+        <v>0.2030984730735996</v>
       </c>
       <c r="C71">
-        <v>-1999.263998203959</v>
+        <v>-2080.438533175422</v>
       </c>
       <c r="D71">
-        <v>2080.149001796042</v>
+        <v>2059.651466824579</v>
       </c>
       <c r="E71">
-        <v>3281.113000000001</v>
+        <v>3341.790000000001</v>
       </c>
       <c r="F71">
-        <v>4186.713000000001</v>
+        <v>4247.390000000001</v>
       </c>
       <c r="G71">
         <v>107.3</v>
@@ -7234,37 +7234,37 @@
         <v>213.4</v>
       </c>
       <c r="M71">
-        <v>840.6919704000002</v>
+        <v>852.8759120000003</v>
       </c>
       <c r="N71">
-        <v>-627.2919704000002</v>
+        <v>-639.4759120000003</v>
       </c>
       <c r="O71">
-        <v>-91.58462767840003</v>
+        <v>-93.36348315200004</v>
       </c>
       <c r="P71">
-        <v>-535.7073427216002</v>
+        <v>-546.1124288480003</v>
       </c>
       <c r="Q71">
-        <v>-510.7073427216002</v>
+        <v>-521.1124288480003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.219778286436153</v>
+        <v>0.2255775626506914</v>
       </c>
       <c r="T71">
-        <v>4.017974282590139</v>
+        <v>4.151906758676476</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.03706042295750229</v>
+        <v>0.03653098834382367</v>
       </c>
       <c r="W71">
-        <v>0.1933582670701335</v>
+        <v>0.1934645775405602</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2538385134075499</v>
+        <v>0.2502122489302991</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2030984730735996</v>
+        <v>0.2046484730735996</v>
       </c>
       <c r="C72">
-        <v>-2080.438533175422</v>
+        <v>-2161.213049454971</v>
       </c>
       <c r="D72">
-        <v>2059.651466824579</v>
+        <v>2039.55395054503</v>
       </c>
       <c r="E72">
-        <v>3341.790000000001</v>
+        <v>3402.467000000001</v>
       </c>
       <c r="F72">
-        <v>4247.390000000001</v>
+        <v>4308.067000000001</v>
       </c>
       <c r="G72">
         <v>107.3</v>
@@ -7316,37 +7316,37 @@
         <v>213.4</v>
       </c>
       <c r="M72">
-        <v>852.8759120000003</v>
+        <v>865.0598536000002</v>
       </c>
       <c r="N72">
-        <v>-639.4759120000003</v>
+        <v>-651.6598536000002</v>
       </c>
       <c r="O72">
-        <v>-93.36348315200004</v>
+        <v>-95.14233862560003</v>
       </c>
       <c r="P72">
-        <v>-546.1124288480003</v>
+        <v>-556.5175149744002</v>
       </c>
       <c r="Q72">
-        <v>-521.1124288480003</v>
+        <v>-531.5175149744002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2255775626506914</v>
+        <v>0.2317767889489911</v>
       </c>
       <c r="T72">
-        <v>4.151906758676476</v>
+        <v>4.295075957251528</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.03653098834382367</v>
+        <v>0.03601646738123462</v>
       </c>
       <c r="W72">
-        <v>0.1934645775405602</v>
+        <v>0.1935678933498481</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2502122489302991</v>
+        <v>0.2466881327481822</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2046484730735996</v>
+        <v>0.2061984730735996</v>
       </c>
       <c r="C73">
-        <v>-2161.21304945497</v>
+        <v>-2241.599143704853</v>
       </c>
       <c r="D73">
-        <v>2039.55395054503</v>
+        <v>2019.844856295148</v>
       </c>
       <c r="E73">
-        <v>3402.467</v>
+        <v>3463.144000000001</v>
       </c>
       <c r="F73">
-        <v>4308.067</v>
+        <v>4368.744000000001</v>
       </c>
       <c r="G73">
         <v>107.3</v>
@@ -7398,37 +7398,37 @@
         <v>213.4</v>
       </c>
       <c r="M73">
-        <v>865.0598536</v>
+        <v>877.2437952000001</v>
       </c>
       <c r="N73">
-        <v>-651.6598536</v>
+        <v>-663.8437952000002</v>
       </c>
       <c r="O73">
-        <v>-95.14233862559999</v>
+        <v>-96.92119409920002</v>
       </c>
       <c r="P73">
-        <v>-556.5175149744</v>
+        <v>-566.9226011008002</v>
       </c>
       <c r="Q73">
-        <v>-531.5175149744</v>
+        <v>-541.9226011008002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.231776788948991</v>
+        <v>0.2384188171257407</v>
       </c>
       <c r="T73">
-        <v>4.295075957251526</v>
+        <v>4.448471527153366</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.03601646738123462</v>
+        <v>0.03551623866760636</v>
       </c>
       <c r="W73">
-        <v>0.1935678933498481</v>
+        <v>0.1936683392755447</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2466881327481824</v>
+        <v>0.2432619086822353</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2061984730735996</v>
+        <v>0.2077484730735995</v>
       </c>
       <c r="C74">
-        <v>-2241.599143704853</v>
+        <v>-2321.607968623231</v>
       </c>
       <c r="D74">
-        <v>2019.844856295148</v>
+        <v>2000.51303137677</v>
       </c>
       <c r="E74">
-        <v>3463.144000000001</v>
+        <v>3523.821</v>
       </c>
       <c r="F74">
-        <v>4368.744000000001</v>
+        <v>4429.421</v>
       </c>
       <c r="G74">
         <v>107.3</v>
@@ -7480,37 +7480,37 @@
         <v>213.4</v>
       </c>
       <c r="M74">
-        <v>877.2437952000001</v>
+        <v>889.4277368</v>
       </c>
       <c r="N74">
-        <v>-663.8437952000002</v>
+        <v>-676.0277368000001</v>
       </c>
       <c r="O74">
-        <v>-96.92119409920002</v>
+        <v>-98.7000495728</v>
       </c>
       <c r="P74">
-        <v>-566.9226011008002</v>
+        <v>-577.3276872272</v>
       </c>
       <c r="Q74">
-        <v>-541.9226011008002</v>
+        <v>-552.3276872272</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2384188171257407</v>
+        <v>0.245552847389657</v>
       </c>
       <c r="T74">
-        <v>4.448471527153366</v>
+        <v>4.61322973186275</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.03551623866760636</v>
+        <v>0.03502971485024189</v>
       </c>
       <c r="W74">
-        <v>0.1936683392755447</v>
+        <v>0.1937660332580714</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2432619086822353</v>
+        <v>0.2399295537687801</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2077484730735995</v>
+        <v>0.2092984730735996</v>
       </c>
       <c r="C75">
-        <v>-2321.607968623231</v>
+        <v>-2401.250253988545</v>
       </c>
       <c r="D75">
-        <v>2000.51303137677</v>
+        <v>1981.547746011455</v>
       </c>
       <c r="E75">
-        <v>3523.821</v>
+        <v>3584.498000000001</v>
       </c>
       <c r="F75">
-        <v>4429.421</v>
+        <v>4490.098000000001</v>
       </c>
       <c r="G75">
         <v>107.3</v>
@@ -7562,37 +7562,37 @@
         <v>213.4</v>
       </c>
       <c r="M75">
-        <v>889.4277368</v>
+        <v>901.6116784000002</v>
       </c>
       <c r="N75">
-        <v>-676.0277368000001</v>
+        <v>-688.2116784000002</v>
       </c>
       <c r="O75">
-        <v>-98.7000495728</v>
+        <v>-100.4789050464</v>
       </c>
       <c r="P75">
-        <v>-577.3276872272</v>
+        <v>-587.7327733536001</v>
       </c>
       <c r="Q75">
-        <v>-552.3276872272</v>
+        <v>-562.7327733536001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.245552847389657</v>
+        <v>0.2532356492123362</v>
       </c>
       <c r="T75">
-        <v>4.61322973186275</v>
+        <v>4.790661644626702</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.03502971485024189</v>
+        <v>0.03455634032523862</v>
       </c>
       <c r="W75">
-        <v>0.1937660332580714</v>
+        <v>0.1938610868626921</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2399295537687801</v>
+        <v>0.2366872625016343</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2092984730735996</v>
+        <v>0.2108484730735996</v>
       </c>
       <c r="C76">
-        <v>-2401.250253988545</v>
+        <v>-2480.536326518093</v>
       </c>
       <c r="D76">
-        <v>1981.547746011455</v>
+        <v>1962.938673481907</v>
       </c>
       <c r="E76">
-        <v>3584.498000000001</v>
+        <v>3645.175000000001</v>
       </c>
       <c r="F76">
-        <v>4490.098000000001</v>
+        <v>4550.775000000001</v>
       </c>
       <c r="G76">
         <v>107.3</v>
@@ -7644,37 +7644,37 @@
         <v>213.4</v>
       </c>
       <c r="M76">
-        <v>901.6116784000002</v>
+        <v>913.7956200000001</v>
       </c>
       <c r="N76">
-        <v>-688.2116784000002</v>
+        <v>-700.3956200000001</v>
       </c>
       <c r="O76">
-        <v>-100.4789050464</v>
+        <v>-102.25776052</v>
       </c>
       <c r="P76">
-        <v>-587.7327733536001</v>
+        <v>-598.1378594800001</v>
       </c>
       <c r="Q76">
-        <v>-562.7327733536001</v>
+        <v>-573.1378594800001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2532356492123362</v>
+        <v>0.2615330751808296</v>
       </c>
       <c r="T76">
-        <v>4.790661644626702</v>
+        <v>4.982288110411771</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.03455634032523862</v>
+        <v>0.0340955891209021</v>
       </c>
       <c r="W76">
-        <v>0.1938610868626921</v>
+        <v>0.1939536057045229</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2366872625016343</v>
+        <v>0.2335314323349459</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2108484730735996</v>
+        <v>0.2123984730735996</v>
       </c>
       <c r="C77">
-        <v>-2480.536326518093</v>
+        <v>-2559.476128618043</v>
       </c>
       <c r="D77">
-        <v>1962.938673481907</v>
+        <v>1944.675871381957</v>
       </c>
       <c r="E77">
-        <v>3645.175000000001</v>
+        <v>3705.852</v>
       </c>
       <c r="F77">
-        <v>4550.775000000001</v>
+        <v>4611.452</v>
       </c>
       <c r="G77">
         <v>107.3</v>
@@ -7726,37 +7726,37 @@
         <v>213.4</v>
       </c>
       <c r="M77">
-        <v>913.7956200000001</v>
+        <v>925.9795616000001</v>
       </c>
       <c r="N77">
-        <v>-700.3956200000001</v>
+        <v>-712.5795616000001</v>
       </c>
       <c r="O77">
-        <v>-102.25776052</v>
+        <v>-104.0366159936</v>
       </c>
       <c r="P77">
-        <v>-598.1378594800001</v>
+        <v>-608.5429456064002</v>
       </c>
       <c r="Q77">
-        <v>-573.1378594800001</v>
+        <v>-583.5429456064002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2615330751808296</v>
+        <v>0.2705219533133642</v>
       </c>
       <c r="T77">
-        <v>4.982288110411771</v>
+        <v>5.189883448345594</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.0340955891209021</v>
+        <v>0.03364696294825865</v>
       </c>
       <c r="W77">
-        <v>0.1939536057045229</v>
+        <v>0.1940436898399897</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2335314323349459</v>
+        <v>0.2304586503305387</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2123984730735996</v>
+        <v>0.2139484730735995</v>
       </c>
       <c r="C78">
-        <v>-2559.476128618043</v>
+        <v>-2638.079236096418</v>
       </c>
       <c r="D78">
-        <v>1944.675871381957</v>
+        <v>1926.749763903583</v>
       </c>
       <c r="E78">
-        <v>3705.852</v>
+        <v>3766.529000000001</v>
       </c>
       <c r="F78">
-        <v>4611.452</v>
+        <v>4672.129000000001</v>
       </c>
       <c r="G78">
         <v>107.3</v>
@@ -7808,37 +7808,37 @@
         <v>213.4</v>
       </c>
       <c r="M78">
-        <v>925.9795616000001</v>
+        <v>938.1635032000002</v>
       </c>
       <c r="N78">
-        <v>-712.5795616000001</v>
+        <v>-724.7635032000002</v>
       </c>
       <c r="O78">
-        <v>-104.0366159936</v>
+        <v>-105.8154714672</v>
       </c>
       <c r="P78">
-        <v>-608.5429456064002</v>
+        <v>-618.9480317328001</v>
       </c>
       <c r="Q78">
-        <v>-583.5429456064002</v>
+        <v>-593.9480317328001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2705219533133642</v>
+        <v>0.2802924730226409</v>
       </c>
       <c r="T78">
-        <v>5.189883448345594</v>
+        <v>5.415530554795402</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.03364696294825865</v>
+        <v>0.03320998940347608</v>
       </c>
       <c r="W78">
-        <v>0.1940436898399897</v>
+        <v>0.194131434127782</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2304586503305387</v>
+        <v>0.2274656808457265</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2139484730735995</v>
+        <v>0.2154984730735995</v>
       </c>
       <c r="C79">
-        <v>-2638.079236096418</v>
+        <v>-2716.354874905356</v>
       </c>
       <c r="D79">
-        <v>1926.749763903583</v>
+        <v>1909.151125094644</v>
       </c>
       <c r="E79">
-        <v>3766.529000000001</v>
+        <v>3827.206000000001</v>
       </c>
       <c r="F79">
-        <v>4672.129000000001</v>
+        <v>4732.806</v>
       </c>
       <c r="G79">
         <v>107.3</v>
@@ -7890,37 +7890,37 @@
         <v>213.4</v>
       </c>
       <c r="M79">
-        <v>938.1635032000002</v>
+        <v>950.3474448000002</v>
       </c>
       <c r="N79">
-        <v>-724.7635032000002</v>
+        <v>-736.9474448000002</v>
       </c>
       <c r="O79">
-        <v>-105.8154714672</v>
+        <v>-107.5943269408</v>
       </c>
       <c r="P79">
-        <v>-618.9480317328001</v>
+        <v>-629.3531178592002</v>
       </c>
       <c r="Q79">
-        <v>-593.9480317328001</v>
+        <v>-604.3531178592002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2802924730226409</v>
+        <v>0.2909512217963973</v>
       </c>
       <c r="T79">
-        <v>5.415530554795402</v>
+        <v>5.66169103455883</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.03320998940347608</v>
+        <v>0.03278422030855972</v>
       </c>
       <c r="W79">
-        <v>0.194131434127782</v>
+        <v>0.1942169285620412</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2274656808457265</v>
+        <v>0.2245494541682173</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2154984730735995</v>
+        <v>0.2170484730735996</v>
       </c>
       <c r="C80">
-        <v>-2716.354874905356</v>
+        <v>-2794.311936974143</v>
       </c>
       <c r="D80">
-        <v>1909.151125094644</v>
+        <v>1891.871063025858</v>
       </c>
       <c r="E80">
-        <v>3827.206000000001</v>
+        <v>3887.883000000001</v>
       </c>
       <c r="F80">
-        <v>4732.806</v>
+        <v>4793.483000000001</v>
       </c>
       <c r="G80">
         <v>107.3</v>
@@ -7972,37 +7972,37 @@
         <v>213.4</v>
       </c>
       <c r="M80">
-        <v>950.3474448000002</v>
+        <v>962.5313864000002</v>
       </c>
       <c r="N80">
-        <v>-736.9474448000002</v>
+        <v>-749.1313864000002</v>
       </c>
       <c r="O80">
-        <v>-107.5943269408</v>
+        <v>-109.3731824144</v>
       </c>
       <c r="P80">
-        <v>-629.3531178592002</v>
+        <v>-639.7582039856002</v>
       </c>
       <c r="Q80">
-        <v>-604.3531178592002</v>
+        <v>-614.7582039856002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2909512217963973</v>
+        <v>0.3026250895009877</v>
       </c>
       <c r="T80">
-        <v>5.66169103455883</v>
+        <v>5.931295369537823</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.03278422030855972</v>
+        <v>0.03236923017807162</v>
       </c>
       <c r="W80">
-        <v>0.1942169285620412</v>
+        <v>0.1943002585802432</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2245494541682173</v>
+        <v>0.2217070560141892</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2170484730735996</v>
+        <v>0.2185984730735996</v>
       </c>
       <c r="C81">
-        <v>-2794.311936974143</v>
+        <v>-2871.958995190115</v>
       </c>
       <c r="D81">
-        <v>1891.871063025858</v>
+        <v>1874.901004809885</v>
       </c>
       <c r="E81">
-        <v>3887.883000000001</v>
+        <v>3948.560000000001</v>
       </c>
       <c r="F81">
-        <v>4793.483000000001</v>
+        <v>4854.160000000001</v>
       </c>
       <c r="G81">
         <v>107.3</v>
@@ -8054,37 +8054,37 @@
         <v>213.4</v>
       </c>
       <c r="M81">
-        <v>962.5313864000002</v>
+        <v>974.7153280000002</v>
       </c>
       <c r="N81">
-        <v>-749.1313864000002</v>
+        <v>-761.3153280000002</v>
       </c>
       <c r="O81">
-        <v>-109.3731824144</v>
+        <v>-111.152037888</v>
       </c>
       <c r="P81">
-        <v>-639.7582039856002</v>
+        <v>-650.1632901120003</v>
       </c>
       <c r="Q81">
-        <v>-614.7582039856002</v>
+        <v>-625.1632901120003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3026250895009877</v>
+        <v>0.3154663439760371</v>
       </c>
       <c r="T81">
-        <v>5.931295369537823</v>
+        <v>6.227860138014714</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.03236923017807162</v>
+        <v>0.03196461480084572</v>
       </c>
       <c r="W81">
-        <v>0.1943002585802432</v>
+        <v>0.1943815053479902</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2217070560141892</v>
+        <v>0.2189357178140118</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2185984730735996</v>
+        <v>0.2201484730735996</v>
       </c>
       <c r="C82">
-        <v>-2871.958995190115</v>
+        <v>-2949.304317580462</v>
       </c>
       <c r="D82">
-        <v>1874.901004809885</v>
+        <v>1858.23268241954</v>
       </c>
       <c r="E82">
-        <v>3948.560000000001</v>
+        <v>4009.237000000001</v>
       </c>
       <c r="F82">
-        <v>4854.160000000001</v>
+        <v>4914.837000000001</v>
       </c>
       <c r="G82">
         <v>107.3</v>
@@ -8136,37 +8136,37 @@
         <v>213.4</v>
       </c>
       <c r="M82">
-        <v>974.7153280000002</v>
+        <v>986.8992696000003</v>
       </c>
       <c r="N82">
-        <v>-761.3153280000002</v>
+        <v>-773.4992696000003</v>
       </c>
       <c r="O82">
-        <v>-111.152037888</v>
+        <v>-112.9308933616</v>
       </c>
       <c r="P82">
-        <v>-650.1632901120003</v>
+        <v>-660.5683762384002</v>
       </c>
       <c r="Q82">
-        <v>-625.1632901120003</v>
+        <v>-635.5683762384002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3154663439760371</v>
+        <v>0.3296593094484601</v>
       </c>
       <c r="T82">
-        <v>6.227860138014714</v>
+        <v>6.555642250541804</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.03196461480084572</v>
+        <v>0.03156998992676121</v>
       </c>
       <c r="W82">
-        <v>0.1943815053479902</v>
+        <v>0.1944607460227064</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2189357178140118</v>
+        <v>0.2162328077175425</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2201484730735996</v>
+        <v>0.2216984730735995</v>
       </c>
       <c r="C83">
-        <v>-2949.304317580462</v>
+        <v>-3026.355880744208</v>
       </c>
       <c r="D83">
-        <v>1858.23268241954</v>
+        <v>1841.858119255793</v>
       </c>
       <c r="E83">
-        <v>4009.237000000001</v>
+        <v>4069.914000000001</v>
       </c>
       <c r="F83">
-        <v>4914.837000000001</v>
+        <v>4975.514000000001</v>
       </c>
       <c r="G83">
         <v>107.3</v>
@@ -8218,37 +8218,37 @@
         <v>213.4</v>
       </c>
       <c r="M83">
-        <v>986.8992696000003</v>
+        <v>999.0832112000003</v>
       </c>
       <c r="N83">
-        <v>-773.4992696000003</v>
+        <v>-785.6832112000003</v>
       </c>
       <c r="O83">
-        <v>-112.9308933616</v>
+        <v>-114.7097488352</v>
       </c>
       <c r="P83">
-        <v>-660.5683762384002</v>
+        <v>-670.9734623648003</v>
       </c>
       <c r="Q83">
-        <v>-635.5683762384002</v>
+        <v>-645.9734623648003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3296593094484601</v>
+        <v>0.3454292710844856</v>
       </c>
       <c r="T83">
-        <v>6.555642250541804</v>
+        <v>6.919844597794127</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.03156998992676121</v>
+        <v>0.03118499004960558</v>
       </c>
       <c r="W83">
-        <v>0.1944607460227064</v>
+        <v>0.1945380539980392</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2162328077175425</v>
+        <v>0.2135958222575725</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2216984730735995</v>
+        <v>0.2232484730735996</v>
       </c>
       <c r="C84">
-        <v>-3026.355880744208</v>
+        <v>-3103.121382580244</v>
       </c>
       <c r="D84">
-        <v>1841.858119255793</v>
+        <v>1825.769617419756</v>
       </c>
       <c r="E84">
-        <v>4069.914000000001</v>
+        <v>4130.591</v>
       </c>
       <c r="F84">
-        <v>4975.514000000001</v>
+        <v>5036.191000000001</v>
       </c>
       <c r="G84">
         <v>107.3</v>
@@ -8300,37 +8300,37 @@
         <v>213.4</v>
       </c>
       <c r="M84">
-        <v>999.0832112000003</v>
+        <v>1011.2671528</v>
       </c>
       <c r="N84">
-        <v>-785.6832112000003</v>
+        <v>-797.8671528000002</v>
       </c>
       <c r="O84">
-        <v>-114.7097488352</v>
+        <v>-116.4886043088</v>
       </c>
       <c r="P84">
-        <v>-670.9734623648003</v>
+        <v>-681.3785484912001</v>
       </c>
       <c r="Q84">
-        <v>-645.9734623648003</v>
+        <v>-656.3785484912001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3454292710844856</v>
+        <v>0.3630545223247496</v>
       </c>
       <c r="T84">
-        <v>6.919844597794127</v>
+        <v>7.326894280017313</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.03118499004960558</v>
+        <v>0.03080926727792359</v>
       </c>
       <c r="W84">
-        <v>0.1945380539980392</v>
+        <v>0.1946134991305929</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2135958222575725</v>
+        <v>0.211022378615915</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2232484730735996</v>
+        <v>0.2247984730735996</v>
       </c>
       <c r="C85">
-        <v>-3103.121382580244</v>
+        <v>-3179.608254354051</v>
       </c>
       <c r="D85">
-        <v>1825.769617419756</v>
+        <v>1809.959745645951</v>
       </c>
       <c r="E85">
-        <v>4130.591</v>
+        <v>4191.268000000001</v>
       </c>
       <c r="F85">
-        <v>5036.191000000001</v>
+        <v>5096.868000000001</v>
       </c>
       <c r="G85">
         <v>107.3</v>
@@ -8382,37 +8382,37 @@
         <v>213.4</v>
       </c>
       <c r="M85">
-        <v>1011.2671528</v>
+        <v>1023.4510944</v>
       </c>
       <c r="N85">
-        <v>-797.8671528000002</v>
+        <v>-810.0510944000004</v>
       </c>
       <c r="O85">
-        <v>-116.4886043088</v>
+        <v>-118.2674597824</v>
       </c>
       <c r="P85">
-        <v>-681.3785484912001</v>
+        <v>-691.7836346176003</v>
       </c>
       <c r="Q85">
-        <v>-656.3785484912001</v>
+        <v>-666.7836346176003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3630545223247496</v>
+        <v>0.3828829299700465</v>
       </c>
       <c r="T85">
-        <v>7.326894280017313</v>
+        <v>7.784825172518396</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.03080926727792359</v>
+        <v>0.03044249028651973</v>
       </c>
       <c r="W85">
-        <v>0.1946134991305929</v>
+        <v>0.1946871479504668</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.211022378615915</v>
+        <v>0.208510207441916</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2247984730735995</v>
+        <v>0.2263484730735996</v>
       </c>
       <c r="C86">
-        <v>-3179.60825435405</v>
+        <v>-3255.82367214287</v>
       </c>
       <c r="D86">
-        <v>1809.959745645951</v>
+        <v>1794.42132785713</v>
       </c>
       <c r="E86">
-        <v>4191.268</v>
+        <v>4251.945</v>
       </c>
       <c r="F86">
-        <v>5096.868</v>
+        <v>5157.545</v>
       </c>
       <c r="G86">
         <v>107.3</v>
@@ -8464,37 +8464,37 @@
         <v>213.4</v>
       </c>
       <c r="M86">
-        <v>1023.4510944</v>
+        <v>1035.635036</v>
       </c>
       <c r="N86">
-        <v>-810.0510944000001</v>
+        <v>-822.2350360000002</v>
       </c>
       <c r="O86">
-        <v>-118.2674597824</v>
+        <v>-120.046315256</v>
       </c>
       <c r="P86">
-        <v>-691.7836346176001</v>
+        <v>-702.1887207440002</v>
       </c>
       <c r="Q86">
-        <v>-666.7836346176001</v>
+        <v>-677.1887207440002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3828829299700462</v>
+        <v>0.4053551253013827</v>
       </c>
       <c r="T86">
-        <v>7.78482517251839</v>
+        <v>8.30381351735295</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.03044249028651974</v>
+        <v>0.03008434334197245</v>
       </c>
       <c r="W86">
-        <v>0.1946871479504668</v>
+        <v>0.194759063856932</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.208510207441916</v>
+        <v>0.2060571461778935</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2263484730735996</v>
+        <v>0.2278984730735996</v>
       </c>
       <c r="C87">
-        <v>-3255.82367214287</v>
+        <v>-3331.774567696373</v>
       </c>
       <c r="D87">
-        <v>1794.42132785713</v>
+        <v>1779.147432303627</v>
       </c>
       <c r="E87">
-        <v>4251.945</v>
+        <v>4312.622</v>
       </c>
       <c r="F87">
-        <v>5157.545</v>
+        <v>5218.222000000001</v>
       </c>
       <c r="G87">
         <v>107.3</v>
@@ -8546,37 +8546,37 @@
         <v>213.4</v>
       </c>
       <c r="M87">
-        <v>1035.635036</v>
+        <v>1047.8189776</v>
       </c>
       <c r="N87">
-        <v>-822.2350360000002</v>
+        <v>-834.4189776000002</v>
       </c>
       <c r="O87">
-        <v>-120.046315256</v>
+        <v>-121.8251707296</v>
       </c>
       <c r="P87">
-        <v>-702.1887207440002</v>
+        <v>-712.5938068704002</v>
       </c>
       <c r="Q87">
-        <v>-677.1887207440002</v>
+        <v>-687.5938068704002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4053551253013827</v>
+        <v>0.4310376342514814</v>
       </c>
       <c r="T87">
-        <v>8.30381351735295</v>
+        <v>8.896943054306732</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.03008434334197245</v>
+        <v>0.02973452539613556</v>
       </c>
       <c r="W87">
-        <v>0.194759063856932</v>
+        <v>0.194829307300456</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2060571461778935</v>
+        <v>0.2036611328502436</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2278984730735996</v>
+        <v>0.2294484730735996</v>
       </c>
       <c r="C88">
-        <v>-3331.774567696373</v>
+        <v>-3407.467638747317</v>
       </c>
       <c r="D88">
-        <v>1779.147432303627</v>
+        <v>1764.131361252683</v>
       </c>
       <c r="E88">
-        <v>4312.622</v>
+        <v>4373.299</v>
       </c>
       <c r="F88">
-        <v>5218.222000000001</v>
+        <v>5278.899</v>
       </c>
       <c r="G88">
         <v>107.3</v>
@@ -8628,37 +8628,37 @@
         <v>213.4</v>
       </c>
       <c r="M88">
-        <v>1047.8189776</v>
+        <v>1060.0029192</v>
       </c>
       <c r="N88">
-        <v>-834.4189776000002</v>
+        <v>-846.6029192000002</v>
       </c>
       <c r="O88">
-        <v>-121.8251707296</v>
+        <v>-123.6040262032</v>
       </c>
       <c r="P88">
-        <v>-712.5938068704002</v>
+        <v>-722.9988929968001</v>
       </c>
       <c r="Q88">
-        <v>-687.5938068704002</v>
+        <v>-697.9988929968001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4310376342514814</v>
+        <v>0.4606712984246724</v>
       </c>
       <c r="T88">
-        <v>8.896943054306732</v>
+        <v>9.581323289253405</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.02973452539613556</v>
+        <v>0.02939274924215699</v>
       </c>
       <c r="W88">
-        <v>0.194829307300456</v>
+        <v>0.1948979359521749</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2036611328502436</v>
+        <v>0.2013202002887464</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2294484730735996</v>
+        <v>0.2620085559023244</v>
       </c>
       <c r="C89">
-        <v>-3407.467638747317</v>
+        <v>-3733.815268678763</v>
       </c>
       <c r="D89">
-        <v>1764.131361252683</v>
+        <v>1498.460731321238</v>
       </c>
       <c r="E89">
-        <v>4373.299</v>
+        <v>4433.976000000001</v>
       </c>
       <c r="F89">
-        <v>5278.899</v>
+        <v>5339.576000000001</v>
       </c>
       <c r="G89">
         <v>107.3</v>
@@ -8710,45 +8710,45 @@
         <v>213.4</v>
       </c>
       <c r="M89">
-        <v>1060.0029192</v>
+        <v>1259.0720208</v>
       </c>
       <c r="N89">
-        <v>-846.6029192000002</v>
+        <v>-1045.6720208</v>
       </c>
       <c r="O89">
-        <v>-123.6040262032</v>
+        <v>-152.6681150368</v>
       </c>
       <c r="P89">
-        <v>-722.9988929968001</v>
+        <v>-893.0039057632001</v>
       </c>
       <c r="Q89">
-        <v>-697.9988929968001</v>
+        <v>-868.0039057632001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4606712984246724</v>
+        <v>0.4969945968661022</v>
       </c>
       <c r="T89">
-        <v>9.581323289253405</v>
+        <v>10.42019854194232</v>
       </c>
       <c r="U89">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02939274924215699</v>
+        <v>0.02474552645543149</v>
       </c>
       <c r="W89">
-        <v>0.1948979359521749</v>
+        <v>0.2299650048618093</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.2013202002887464</v>
+        <v>0.1694899072289829</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2620085559023244</v>
+        <v>0.2639085559023244</v>
       </c>
       <c r="C90">
-        <v>-3733.815268678763</v>
+        <v>-3807.545747382208</v>
       </c>
       <c r="D90">
-        <v>1498.460731321238</v>
+        <v>1485.407252617792</v>
       </c>
       <c r="E90">
-        <v>4433.976000000001</v>
+        <v>4494.653</v>
       </c>
       <c r="F90">
-        <v>5339.576000000001</v>
+        <v>5400.253000000001</v>
       </c>
       <c r="G90">
         <v>107.3</v>
@@ -8792,37 +8792,37 @@
         <v>213.4</v>
       </c>
       <c r="M90">
-        <v>1259.0720208</v>
+        <v>1273.3796574</v>
       </c>
       <c r="N90">
-        <v>-1045.6720208</v>
+        <v>-1059.9796574</v>
       </c>
       <c r="O90">
-        <v>-152.6681150368</v>
+        <v>-154.7570299804</v>
       </c>
       <c r="P90">
-        <v>-893.0039057632001</v>
+        <v>-905.2226274196001</v>
       </c>
       <c r="Q90">
-        <v>-868.0039057632001</v>
+        <v>-880.2226274196001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4969945968661022</v>
+        <v>0.5380122874902933</v>
       </c>
       <c r="T90">
-        <v>10.42019854194232</v>
+        <v>11.36748931848253</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02474552645543149</v>
+        <v>0.02446748683233676</v>
       </c>
       <c r="W90">
-        <v>0.2299650048618093</v>
+        <v>0.230030566604935</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1694899072289829</v>
+        <v>0.167585526248882</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2639085559023244</v>
+        <v>0.2658085559023244</v>
       </c>
       <c r="C91">
-        <v>-3807.545747382208</v>
+        <v>-3881.050765676311</v>
       </c>
       <c r="D91">
-        <v>1485.407252617792</v>
+        <v>1472.579234323691</v>
       </c>
       <c r="E91">
-        <v>4494.653</v>
+        <v>4555.330000000001</v>
       </c>
       <c r="F91">
-        <v>5400.253000000001</v>
+        <v>5460.930000000001</v>
       </c>
       <c r="G91">
         <v>107.3</v>
@@ -8874,37 +8874,37 @@
         <v>213.4</v>
       </c>
       <c r="M91">
-        <v>1273.3796574</v>
+        <v>1287.687294</v>
       </c>
       <c r="N91">
-        <v>-1059.9796574</v>
+        <v>-1074.287294</v>
       </c>
       <c r="O91">
-        <v>-154.7570299804</v>
+        <v>-156.845944924</v>
       </c>
       <c r="P91">
-        <v>-905.2226274196001</v>
+        <v>-917.4413490760002</v>
       </c>
       <c r="Q91">
-        <v>-880.2226274196001</v>
+        <v>-892.4413490760002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5380122874902933</v>
+        <v>0.5872335162393226</v>
       </c>
       <c r="T91">
-        <v>11.36748931848253</v>
+        <v>12.50423825033078</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02446748683233676</v>
+        <v>0.02419562586753302</v>
       </c>
       <c r="W91">
-        <v>0.230030566604935</v>
+        <v>0.2300946714204357</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.167585526248882</v>
+        <v>0.1657234648461167</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2658085559023244</v>
+        <v>0.2677085559023244</v>
       </c>
       <c r="C92">
-        <v>-3881.050765676311</v>
+        <v>-3954.336114794884</v>
       </c>
       <c r="D92">
-        <v>1472.579234323691</v>
+        <v>1459.970885205118</v>
       </c>
       <c r="E92">
-        <v>4555.330000000001</v>
+        <v>4616.007000000001</v>
       </c>
       <c r="F92">
-        <v>5460.930000000001</v>
+        <v>5521.607000000001</v>
       </c>
       <c r="G92">
         <v>107.3</v>
@@ -8956,37 +8956,37 @@
         <v>213.4</v>
       </c>
       <c r="M92">
-        <v>1287.687294</v>
+        <v>1301.9949306</v>
       </c>
       <c r="N92">
-        <v>-1074.287294</v>
+        <v>-1088.5949306</v>
       </c>
       <c r="O92">
-        <v>-156.845944924</v>
+        <v>-158.9348598676</v>
       </c>
       <c r="P92">
-        <v>-917.4413490760002</v>
+        <v>-929.6600707324002</v>
       </c>
       <c r="Q92">
-        <v>-892.4413490760002</v>
+        <v>-904.6600707324002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5872335162393226</v>
+        <v>0.6473927958214697</v>
       </c>
       <c r="T92">
-        <v>12.50423825033078</v>
+        <v>13.89359805592309</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02419562586753302</v>
+        <v>0.0239297398689887</v>
       </c>
       <c r="W92">
-        <v>0.2300946714204357</v>
+        <v>0.2301573673388925</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1657234648461167</v>
+        <v>0.1639023278697856</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2677085559023244</v>
+        <v>0.2696085559023244</v>
       </c>
       <c r="C93">
-        <v>-3954.336114794884</v>
+        <v>-4027.407389315382</v>
       </c>
       <c r="D93">
-        <v>1459.970885205118</v>
+        <v>1447.576610684619</v>
       </c>
       <c r="E93">
-        <v>4616.007000000001</v>
+        <v>4676.684</v>
       </c>
       <c r="F93">
-        <v>5521.607000000001</v>
+        <v>5582.284000000001</v>
       </c>
       <c r="G93">
         <v>107.3</v>
@@ -9038,37 +9038,37 @@
         <v>213.4</v>
       </c>
       <c r="M93">
-        <v>1301.9949306</v>
+        <v>1316.3025672</v>
       </c>
       <c r="N93">
-        <v>-1088.5949306</v>
+        <v>-1102.9025672</v>
       </c>
       <c r="O93">
-        <v>-158.9348598676</v>
+        <v>-161.0237748112</v>
       </c>
       <c r="P93">
-        <v>-929.6600707324002</v>
+        <v>-941.8787923888001</v>
       </c>
       <c r="Q93">
-        <v>-904.6600707324002</v>
+        <v>-916.8787923888001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6473927958214697</v>
+        <v>0.7225918952991536</v>
       </c>
       <c r="T93">
-        <v>13.89359805592309</v>
+        <v>15.63029781291348</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0239297398689887</v>
+        <v>0.02366963400084752</v>
       </c>
       <c r="W93">
-        <v>0.2301573673388925</v>
+        <v>0.2302187003026002</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1639023278697856</v>
+        <v>0.1621207808277229</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2696085559023244</v>
+        <v>0.2715085559023244</v>
       </c>
       <c r="C94">
-        <v>-4027.407389315382</v>
+        <v>-4100.269995436096</v>
       </c>
       <c r="D94">
-        <v>1447.576610684619</v>
+        <v>1435.391004563905</v>
       </c>
       <c r="E94">
-        <v>4676.684</v>
+        <v>4737.361000000001</v>
       </c>
       <c r="F94">
-        <v>5582.284000000001</v>
+        <v>5642.961000000001</v>
       </c>
       <c r="G94">
         <v>107.3</v>
@@ -9120,37 +9120,37 @@
         <v>213.4</v>
       </c>
       <c r="M94">
-        <v>1316.3025672</v>
+        <v>1330.6102038</v>
       </c>
       <c r="N94">
-        <v>-1102.9025672</v>
+        <v>-1117.2102038</v>
       </c>
       <c r="O94">
-        <v>-161.0237748112</v>
+        <v>-163.1126897548</v>
       </c>
       <c r="P94">
-        <v>-941.8787923888001</v>
+        <v>-954.0975140452002</v>
       </c>
       <c r="Q94">
-        <v>-916.8787923888001</v>
+        <v>-929.0975140452002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7225918952991536</v>
+        <v>0.8192764517704613</v>
       </c>
       <c r="T94">
-        <v>15.63029781291348</v>
+        <v>17.86319750047255</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02366963400084752</v>
+        <v>0.02341512180729002</v>
       </c>
       <c r="W94">
-        <v>0.2302187003026002</v>
+        <v>0.230278714277841</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1621207808277229</v>
+        <v>0.1603775466252741</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2715085559023244</v>
+        <v>0.2734085559023244</v>
       </c>
       <c r="C95">
-        <v>-4100.269995436096</v>
+        <v>-4172.929158838783</v>
       </c>
       <c r="D95">
-        <v>1435.391004563905</v>
+        <v>1423.408841161217</v>
       </c>
       <c r="E95">
-        <v>4737.361000000001</v>
+        <v>4798.038</v>
       </c>
       <c r="F95">
-        <v>5642.961000000001</v>
+        <v>5703.638000000001</v>
       </c>
       <c r="G95">
         <v>107.3</v>
@@ -9202,37 +9202,37 @@
         <v>213.4</v>
       </c>
       <c r="M95">
-        <v>1330.6102038</v>
+        <v>1344.9178404</v>
       </c>
       <c r="N95">
-        <v>-1117.2102038</v>
+        <v>-1131.5178404</v>
       </c>
       <c r="O95">
-        <v>-163.1126897548</v>
+        <v>-165.2016046984</v>
       </c>
       <c r="P95">
-        <v>-954.0975140452002</v>
+        <v>-966.3162357016001</v>
       </c>
       <c r="Q95">
-        <v>-929.0975140452002</v>
+        <v>-941.3162357016001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8192764517704613</v>
+        <v>0.9481891937322048</v>
       </c>
       <c r="T95">
-        <v>17.86319750047255</v>
+        <v>20.84039708388464</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02341512180729002</v>
+        <v>0.02316602476678693</v>
       </c>
       <c r="W95">
-        <v>0.230278714277841</v>
+        <v>0.2303374513599916</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1603775466252741</v>
+        <v>0.1586714025122393</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2734085559023244</v>
+        <v>0.2753085559023244</v>
       </c>
       <c r="C96">
-        <v>-4172.929158838783</v>
+        <v>-4245.389932160757</v>
       </c>
       <c r="D96">
-        <v>1423.408841161217</v>
+        <v>1411.625067839245</v>
       </c>
       <c r="E96">
-        <v>4798.038</v>
+        <v>4858.715000000001</v>
       </c>
       <c r="F96">
-        <v>5703.638000000001</v>
+        <v>5764.315000000001</v>
       </c>
       <c r="G96">
         <v>107.3</v>
@@ -9284,37 +9284,37 @@
         <v>213.4</v>
       </c>
       <c r="M96">
-        <v>1344.9178404</v>
+        <v>1359.225477</v>
       </c>
       <c r="N96">
-        <v>-1131.5178404</v>
+        <v>-1145.825477</v>
       </c>
       <c r="O96">
-        <v>-165.2016046984</v>
+        <v>-167.290519642</v>
       </c>
       <c r="P96">
-        <v>-966.3162357016001</v>
+        <v>-978.5349573580003</v>
       </c>
       <c r="Q96">
-        <v>-941.3162357016001</v>
+        <v>-953.5349573580003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9481891937322048</v>
+        <v>1.128667032478647</v>
       </c>
       <c r="T96">
-        <v>20.84039708388464</v>
+        <v>25.00847650066159</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02316602476678693</v>
+        <v>0.02292217187450496</v>
       </c>
       <c r="W96">
-        <v>0.2303374513599916</v>
+        <v>0.2303949518719917</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1586714025122393</v>
+        <v>0.1570011772226368</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2753085559023244</v>
+        <v>0.2772085559023244</v>
       </c>
       <c r="C97">
-        <v>-4245.389932160757</v>
+        <v>-4317.65720209886</v>
       </c>
       <c r="D97">
-        <v>1411.625067839245</v>
+        <v>1400.034797901141</v>
       </c>
       <c r="E97">
-        <v>4858.715000000001</v>
+        <v>4919.392000000001</v>
       </c>
       <c r="F97">
-        <v>5764.315000000001</v>
+        <v>5824.992000000001</v>
       </c>
       <c r="G97">
         <v>107.3</v>
@@ -9366,37 +9366,37 @@
         <v>213.4</v>
       </c>
       <c r="M97">
-        <v>1359.225477</v>
+        <v>1373.5331136</v>
       </c>
       <c r="N97">
-        <v>-1145.825477</v>
+        <v>-1160.1331136</v>
       </c>
       <c r="O97">
-        <v>-167.290519642</v>
+        <v>-169.3794345856</v>
       </c>
       <c r="P97">
-        <v>-978.5349573580003</v>
+        <v>-990.7536790144002</v>
       </c>
       <c r="Q97">
-        <v>-953.5349573580003</v>
+        <v>-965.7536790144002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.128667032478647</v>
+        <v>1.399383790598309</v>
       </c>
       <c r="T97">
-        <v>25.00847650066159</v>
+        <v>31.260595625827</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02292217187450496</v>
+        <v>0.0226833992508122</v>
       </c>
       <c r="W97">
-        <v>0.2303949518719917</v>
+        <v>0.2304512544566585</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1570011772226368</v>
+        <v>0.1553657482932344</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2772085559023244</v>
+        <v>0.2791085559023244</v>
       </c>
       <c r="C98">
-        <v>-4317.657202098859</v>
+        <v>-4389.735696166337</v>
       </c>
       <c r="D98">
-        <v>1400.034797901141</v>
+        <v>1388.633303833664</v>
       </c>
       <c r="E98">
-        <v>4919.392</v>
+        <v>4980.069</v>
       </c>
       <c r="F98">
-        <v>5824.992</v>
+        <v>5885.669000000001</v>
       </c>
       <c r="G98">
         <v>107.3</v>
@@ -9448,37 +9448,37 @@
         <v>213.4</v>
       </c>
       <c r="M98">
-        <v>1373.5331136</v>
+        <v>1387.8407502</v>
       </c>
       <c r="N98">
-        <v>-1160.1331136</v>
+        <v>-1174.4407502</v>
       </c>
       <c r="O98">
-        <v>-169.3794345856</v>
+        <v>-171.4683495292</v>
       </c>
       <c r="P98">
-        <v>-990.7536790144002</v>
+        <v>-1002.9724006708</v>
       </c>
       <c r="Q98">
-        <v>-965.7536790144002</v>
+        <v>-977.9724006708002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.399383790598305</v>
+        <v>1.850578387464407</v>
       </c>
       <c r="T98">
-        <v>31.26059562582692</v>
+        <v>41.68079416776923</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0226833992508122</v>
+        <v>0.02244954977399971</v>
       </c>
       <c r="W98">
-        <v>0.2304512544566585</v>
+        <v>0.2305063961632909</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1553657482932344</v>
+        <v>0.1537640395479433</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2791085559023244</v>
+        <v>0.2810085559023244</v>
       </c>
       <c r="C99">
-        <v>-4389.735696166337</v>
+        <v>-4461.629989122209</v>
       </c>
       <c r="D99">
-        <v>1388.633303833664</v>
+        <v>1377.416010877791</v>
       </c>
       <c r="E99">
-        <v>4980.069</v>
+        <v>5040.746</v>
       </c>
       <c r="F99">
-        <v>5885.669000000001</v>
+        <v>5946.346</v>
       </c>
       <c r="G99">
         <v>107.3</v>
@@ -9530,37 +9530,37 @@
         <v>213.4</v>
       </c>
       <c r="M99">
-        <v>1387.8407502</v>
+        <v>1402.1483868</v>
       </c>
       <c r="N99">
-        <v>-1174.4407502</v>
+        <v>-1188.7483868</v>
       </c>
       <c r="O99">
-        <v>-171.4683495292</v>
+        <v>-173.5572644728</v>
       </c>
       <c r="P99">
-        <v>-1002.9724006708</v>
+        <v>-1015.1911223272</v>
       </c>
       <c r="Q99">
-        <v>-977.9724006708002</v>
+        <v>-990.1911223272002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.850578387464407</v>
+        <v>2.75296758119661</v>
       </c>
       <c r="T99">
-        <v>41.68079416776923</v>
+        <v>62.52119125165383</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02244954977399971</v>
+        <v>0.02222047273548951</v>
       </c>
       <c r="W99">
-        <v>0.2305063961632909</v>
+        <v>0.2305604125289716</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1537640395479433</v>
+        <v>0.1521950187362295</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2810085559023244</v>
+        <v>0.2829085559023244</v>
       </c>
       <c r="C100">
-        <v>-4461.629989122209</v>
+        <v>-4533.344509091527</v>
       </c>
       <c r="D100">
-        <v>1377.416010877791</v>
+        <v>1366.378490908475</v>
       </c>
       <c r="E100">
-        <v>5040.746</v>
+        <v>5101.423000000001</v>
       </c>
       <c r="F100">
-        <v>5946.346</v>
+        <v>6007.023000000001</v>
       </c>
       <c r="G100">
         <v>107.3</v>
@@ -9612,37 +9612,37 @@
         <v>213.4</v>
       </c>
       <c r="M100">
-        <v>1402.1483868</v>
+        <v>1416.4560234</v>
       </c>
       <c r="N100">
-        <v>-1188.7483868</v>
+        <v>-1203.0560234</v>
       </c>
       <c r="O100">
-        <v>-173.5572644728</v>
+        <v>-175.6461794164</v>
       </c>
       <c r="P100">
-        <v>-1015.1911223272</v>
+        <v>-1027.4098439836</v>
       </c>
       <c r="Q100">
-        <v>-990.1911223272002</v>
+        <v>-1002.4098439836</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.75296758119661</v>
+        <v>5.460135162393221</v>
       </c>
       <c r="T100">
-        <v>62.52119125165383</v>
+        <v>125.0423825033077</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02222047273548951</v>
+        <v>0.02199602351593911</v>
       </c>
       <c r="W100">
-        <v>0.2305604125289716</v>
+        <v>0.2306133376549416</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1521950187362295</v>
+        <v>0.1506576953146515</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2829085559023244</v>
-      </c>
-      <c r="C101">
-        <v>-4533.344509091527</v>
-      </c>
-      <c r="D101">
-        <v>1366.378490908475</v>
-      </c>
-      <c r="E101">
-        <v>5101.423000000001</v>
-      </c>
-      <c r="F101">
-        <v>6007.023000000001</v>
-      </c>
-      <c r="G101">
-        <v>107.3</v>
-      </c>
-      <c r="H101">
-        <v>5162.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>238.4</v>
-      </c>
-      <c r="K101">
-        <v>25</v>
-      </c>
-      <c r="L101">
-        <v>213.4</v>
-      </c>
-      <c r="M101">
-        <v>1416.4560234</v>
-      </c>
-      <c r="N101">
-        <v>-1203.0560234</v>
-      </c>
-      <c r="O101">
-        <v>-175.6461794164</v>
-      </c>
-      <c r="P101">
-        <v>-1027.4098439836</v>
-      </c>
-      <c r="Q101">
-        <v>-1002.4098439836</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.460135162393221</v>
-      </c>
-      <c r="T101">
-        <v>125.0423825033077</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02199602351593911</v>
-      </c>
-      <c r="W101">
-        <v>0.2306133376549416</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1506576953146515</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
